--- a/research/traditional_assets/database/data/iceland/iceland_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_real_estate_development.xlsx
@@ -1258,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1395,22 +1395,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06929738574303698</v>
+        <v>0.0691947909715509</v>
       </c>
       <c r="C2">
-        <v>442.7612491366955</v>
+        <v>439.1559097269111</v>
       </c>
       <c r="D2">
-        <v>417.3612491366956</v>
+        <v>418.3709097269112</v>
       </c>
       <c r="E2">
-        <v>-242.8</v>
+        <v>-238.185</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.615</v>
       </c>
       <c r="G2">
         <v>25.4</v>
@@ -1431,28 +1431,28 @@
         <v>21.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2321345</v>
       </c>
       <c r="N2">
-        <v>21.6</v>
+        <v>21.3678655</v>
       </c>
       <c r="O2">
-        <v>4.32</v>
+        <v>4.2735731</v>
       </c>
       <c r="P2">
-        <v>17.28</v>
+        <v>17.0942924</v>
       </c>
       <c r="Q2">
-        <v>-4.32</v>
+        <v>-4.505707600000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06929738574303698</v>
+        <v>0.06948726360762718</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4493386376512635</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>93.04950362828447</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1477,22 +1477,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0691947909715509</v>
+        <v>0.06909219620006483</v>
       </c>
       <c r="C3">
-        <v>439.1559097269111</v>
+        <v>435.5554672097312</v>
       </c>
       <c r="D3">
-        <v>418.3709097269112</v>
+        <v>419.3854672097312</v>
       </c>
       <c r="E3">
-        <v>-238.185</v>
+        <v>-233.57</v>
       </c>
       <c r="F3">
-        <v>4.615</v>
+        <v>9.23</v>
       </c>
       <c r="G3">
         <v>25.4</v>
@@ -1513,28 +1513,28 @@
         <v>21.6</v>
       </c>
       <c r="M3">
-        <v>0.2321345</v>
+        <v>0.464269</v>
       </c>
       <c r="N3">
-        <v>21.3678655</v>
+        <v>21.135731</v>
       </c>
       <c r="O3">
-        <v>4.2735731</v>
+        <v>4.2271462</v>
       </c>
       <c r="P3">
-        <v>17.0942924</v>
+        <v>16.9085848</v>
       </c>
       <c r="Q3">
-        <v>-4.505707600000001</v>
+        <v>-4.691415200000002</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06948726360762718</v>
+        <v>0.0696810165306784</v>
       </c>
       <c r="T3">
-        <v>0.4493386376512635</v>
+        <v>0.4530140590054107</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>93.04950362828447</v>
+        <v>46.52475181414223</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1559,22 +1559,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06909219620006483</v>
+        <v>0.06898960142857875</v>
       </c>
       <c r="C4">
-        <v>435.5554672097312</v>
+        <v>431.9599572969333</v>
       </c>
       <c r="D4">
-        <v>419.3854672097312</v>
+        <v>420.4049572969334</v>
       </c>
       <c r="E4">
-        <v>-233.57</v>
+        <v>-228.955</v>
       </c>
       <c r="F4">
-        <v>9.23</v>
+        <v>13.845</v>
       </c>
       <c r="G4">
         <v>25.4</v>
@@ -1595,28 +1595,28 @@
         <v>21.6</v>
       </c>
       <c r="M4">
-        <v>0.464269</v>
+        <v>0.6964035</v>
       </c>
       <c r="N4">
-        <v>21.135731</v>
+        <v>20.9035965</v>
       </c>
       <c r="O4">
-        <v>4.2271462</v>
+        <v>4.180719300000001</v>
       </c>
       <c r="P4">
-        <v>16.9085848</v>
+        <v>16.7228772</v>
       </c>
       <c r="Q4">
-        <v>-4.691415200000002</v>
+        <v>-4.877122799999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0696810165306784</v>
+        <v>0.06987876435935954</v>
       </c>
       <c r="T4">
-        <v>0.4530140590054107</v>
+        <v>0.4567652622431485</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.52475181414223</v>
+        <v>31.01650120942816</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1641,22 +1641,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06898960142857875</v>
+        <v>0.06888700665709269</v>
       </c>
       <c r="C5">
-        <v>431.9599572969333</v>
+        <v>428.3694160483898</v>
       </c>
       <c r="D5">
-        <v>420.4049572969334</v>
+        <v>421.4294160483898</v>
       </c>
       <c r="E5">
-        <v>-228.955</v>
+        <v>-224.34</v>
       </c>
       <c r="F5">
-        <v>13.845</v>
+        <v>18.46</v>
       </c>
       <c r="G5">
         <v>25.4</v>
@@ -1677,28 +1677,28 @@
         <v>21.6</v>
       </c>
       <c r="M5">
-        <v>0.6964035</v>
+        <v>0.928538</v>
       </c>
       <c r="N5">
-        <v>20.9035965</v>
+        <v>20.671462</v>
       </c>
       <c r="O5">
-        <v>4.180719300000001</v>
+        <v>4.134292400000001</v>
       </c>
       <c r="P5">
-        <v>16.7228772</v>
+        <v>16.5371696</v>
       </c>
       <c r="Q5">
-        <v>-4.877122799999999</v>
+        <v>-5.062830399999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06987876435935954</v>
+        <v>0.07008063193447155</v>
       </c>
       <c r="T5">
-        <v>0.4567652622431485</v>
+        <v>0.4605946155483393</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.01650120942816</v>
+        <v>23.26237590707112</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06888700665709269</v>
+        <v>0.06878441188560661</v>
       </c>
       <c r="C6">
-        <v>428.3694160483898</v>
+        <v>424.7838798763203</v>
       </c>
       <c r="D6">
-        <v>421.4294160483898</v>
+        <v>422.4588798763203</v>
       </c>
       <c r="E6">
-        <v>-224.34</v>
+        <v>-219.725</v>
       </c>
       <c r="F6">
-        <v>18.46</v>
+        <v>23.075</v>
       </c>
       <c r="G6">
         <v>25.4</v>
@@ -1759,28 +1759,28 @@
         <v>21.6</v>
       </c>
       <c r="M6">
-        <v>0.928538</v>
+        <v>1.1606725</v>
       </c>
       <c r="N6">
-        <v>20.671462</v>
+        <v>20.4393275</v>
       </c>
       <c r="O6">
-        <v>4.134292400000001</v>
+        <v>4.0878655</v>
       </c>
       <c r="P6">
-        <v>16.5371696</v>
+        <v>16.351462</v>
       </c>
       <c r="Q6">
-        <v>-5.062830399999999</v>
+        <v>-5.248538</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07008063193447155</v>
+        <v>0.07028674935327012</v>
       </c>
       <c r="T6">
-        <v>0.4605946155483393</v>
+        <v>0.4645045868178497</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.26237590707112</v>
+        <v>18.60990072565689</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1805,22 +1805,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06878441188560661</v>
+        <v>0.06868181711412052</v>
       </c>
       <c r="C7">
-        <v>424.7838798763203</v>
+        <v>421.203385549605</v>
       </c>
       <c r="D7">
-        <v>422.4588798763203</v>
+        <v>423.493385549605</v>
       </c>
       <c r="E7">
-        <v>-219.725</v>
+        <v>-215.11</v>
       </c>
       <c r="F7">
-        <v>23.075</v>
+        <v>27.69</v>
       </c>
       <c r="G7">
         <v>25.4</v>
@@ -1841,28 +1841,28 @@
         <v>21.6</v>
       </c>
       <c r="M7">
-        <v>1.1606725</v>
+        <v>1.392807</v>
       </c>
       <c r="N7">
-        <v>20.4393275</v>
+        <v>20.207193</v>
       </c>
       <c r="O7">
-        <v>4.0878655</v>
+        <v>4.0414386</v>
       </c>
       <c r="P7">
-        <v>16.351462</v>
+        <v>16.1657544</v>
       </c>
       <c r="Q7">
-        <v>-5.248538</v>
+        <v>-5.434245600000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07028674935327012</v>
+        <v>0.07049725224906439</v>
       </c>
       <c r="T7">
-        <v>0.4645045868178497</v>
+        <v>0.468497748965435</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.60990072565689</v>
+        <v>15.50825060471408</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1887,22 +1887,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06868181711412052</v>
+        <v>0.06857922234263446</v>
       </c>
       <c r="C8">
-        <v>421.203385549605</v>
+        <v>417.6279701981628</v>
       </c>
       <c r="D8">
-        <v>423.493385549605</v>
+        <v>424.5329701981628</v>
       </c>
       <c r="E8">
-        <v>-215.11</v>
+        <v>-210.495</v>
       </c>
       <c r="F8">
-        <v>27.69</v>
+        <v>32.305</v>
       </c>
       <c r="G8">
         <v>25.4</v>
@@ -1923,28 +1923,28 @@
         <v>21.6</v>
       </c>
       <c r="M8">
-        <v>1.392807</v>
+        <v>1.6249415</v>
       </c>
       <c r="N8">
-        <v>20.207193</v>
+        <v>19.9750585</v>
       </c>
       <c r="O8">
-        <v>4.0414386</v>
+        <v>3.995011700000001</v>
       </c>
       <c r="P8">
-        <v>16.1657544</v>
+        <v>15.9800468</v>
       </c>
       <c r="Q8">
-        <v>-5.434245600000001</v>
+        <v>-5.619953199999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07049725224906439</v>
+        <v>0.07071228208885426</v>
       </c>
       <c r="T8">
-        <v>0.468497748965435</v>
+        <v>0.472576785567807</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.50825060471408</v>
+        <v>13.29278623261207</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1969,22 +1969,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06857922234263444</v>
+        <v>0.0685726275711484</v>
       </c>
       <c r="C9">
-        <v>417.6279701981629</v>
+        <v>413.0799691035517</v>
       </c>
       <c r="D9">
-        <v>424.532970198163</v>
+        <v>424.5999691035517</v>
       </c>
       <c r="E9">
-        <v>-210.495</v>
+        <v>-205.88</v>
       </c>
       <c r="F9">
-        <v>32.305</v>
+        <v>36.92</v>
       </c>
       <c r="G9">
         <v>25.4</v>
@@ -2005,45 +2005,45 @@
         <v>21.6</v>
       </c>
       <c r="M9">
-        <v>1.6249415</v>
+        <v>1.912456</v>
       </c>
       <c r="N9">
-        <v>19.9750585</v>
+        <v>19.687544</v>
       </c>
       <c r="O9">
-        <v>3.995011700000001</v>
+        <v>3.937508800000001</v>
       </c>
       <c r="P9">
-        <v>15.9800468</v>
+        <v>15.7500352</v>
       </c>
       <c r="Q9">
-        <v>-5.619953199999999</v>
+        <v>-5.849964799999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07071228208885426</v>
+        <v>0.07093198649037868</v>
       </c>
       <c r="T9">
-        <v>0.472576785567807</v>
+        <v>0.4767444968789262</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.29278623261207</v>
+        <v>11.29437749156059</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2051,22 +2051,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0685726275711484</v>
+        <v>0.06848203279966232</v>
       </c>
       <c r="C10">
-        <v>413.0799691035517</v>
+        <v>409.3875027129568</v>
       </c>
       <c r="D10">
-        <v>424.5999691035517</v>
+        <v>425.5225027129568</v>
       </c>
       <c r="E10">
-        <v>-205.88</v>
+        <v>-201.265</v>
       </c>
       <c r="F10">
-        <v>36.92</v>
+        <v>41.535</v>
       </c>
       <c r="G10">
         <v>25.4</v>
@@ -2087,28 +2087,28 @@
         <v>21.6</v>
       </c>
       <c r="M10">
-        <v>1.912456</v>
+        <v>2.151513</v>
       </c>
       <c r="N10">
-        <v>19.687544</v>
+        <v>19.448487</v>
       </c>
       <c r="O10">
-        <v>3.937508800000001</v>
+        <v>3.8896974</v>
       </c>
       <c r="P10">
-        <v>15.7500352</v>
+        <v>15.5587896</v>
       </c>
       <c r="Q10">
-        <v>-5.849964799999999</v>
+        <v>-6.041210400000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07093198649037868</v>
+        <v>0.07115651956006848</v>
       </c>
       <c r="T10">
-        <v>0.4767444968789262</v>
+        <v>0.4810038062408392</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.29437749156059</v>
+        <v>10.03944665916497</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06848203279966232</v>
+        <v>0.06852743802817625</v>
       </c>
       <c r="C11">
-        <v>409.3875027129568</v>
+        <v>404.3096371847887</v>
       </c>
       <c r="D11">
-        <v>425.5225027129568</v>
+        <v>425.0596371847887</v>
       </c>
       <c r="E11">
-        <v>-201.265</v>
+        <v>-196.65</v>
       </c>
       <c r="F11">
-        <v>41.535</v>
+        <v>46.15</v>
       </c>
       <c r="G11">
         <v>25.4</v>
@@ -2169,45 +2169,45 @@
         <v>21.6</v>
       </c>
       <c r="M11">
-        <v>2.151513</v>
+        <v>2.469025</v>
       </c>
       <c r="N11">
-        <v>19.448487</v>
+        <v>19.130975</v>
       </c>
       <c r="O11">
-        <v>3.8896974</v>
+        <v>3.826195000000001</v>
       </c>
       <c r="P11">
-        <v>15.5587896</v>
+        <v>15.30478</v>
       </c>
       <c r="Q11">
-        <v>-6.041210400000001</v>
+        <v>-6.295219999999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07115651956006848</v>
+        <v>0.07138604225352915</v>
       </c>
       <c r="T11">
-        <v>0.4810038062408392</v>
+        <v>0.4853577669219059</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.03944665916497</v>
+        <v>8.748392584117214</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2215,22 +2215,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06852743802817625</v>
+        <v>0.06845044325669017</v>
       </c>
       <c r="C12">
-        <v>404.3096371847887</v>
+        <v>400.4801248231497</v>
       </c>
       <c r="D12">
-        <v>425.0596371847887</v>
+        <v>425.8451248231497</v>
       </c>
       <c r="E12">
-        <v>-196.65</v>
+        <v>-192.035</v>
       </c>
       <c r="F12">
-        <v>46.15000000000001</v>
+        <v>50.765</v>
       </c>
       <c r="G12">
         <v>25.4</v>
@@ -2251,28 +2251,28 @@
         <v>21.6</v>
       </c>
       <c r="M12">
-        <v>2.469025</v>
+        <v>2.7159275</v>
       </c>
       <c r="N12">
-        <v>19.130975</v>
+        <v>18.8840725</v>
       </c>
       <c r="O12">
-        <v>3.826195</v>
+        <v>3.7768145</v>
       </c>
       <c r="P12">
-        <v>15.30478</v>
+        <v>15.107258</v>
       </c>
       <c r="Q12">
-        <v>-6.295220000000002</v>
+        <v>-6.492742</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07138604225352915</v>
+        <v>0.07162072276032602</v>
       </c>
       <c r="T12">
-        <v>0.485357766921906</v>
+        <v>0.4898095694160302</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.748392584117212</v>
+        <v>7.953084167379285</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2297,22 +2297,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06845044325669017</v>
+        <v>0.06845024848520409</v>
       </c>
       <c r="C13">
-        <v>400.4801248231497</v>
+        <v>395.8671155301375</v>
       </c>
       <c r="D13">
-        <v>425.8451248231497</v>
+        <v>425.8471155301375</v>
       </c>
       <c r="E13">
-        <v>-192.035</v>
+        <v>-187.42</v>
       </c>
       <c r="F13">
-        <v>50.765</v>
+        <v>55.38</v>
       </c>
       <c r="G13">
         <v>25.4</v>
@@ -2333,45 +2333,45 @@
         <v>21.6</v>
       </c>
       <c r="M13">
-        <v>2.7159275</v>
+        <v>3.007134</v>
       </c>
       <c r="N13">
-        <v>18.8840725</v>
+        <v>18.592866</v>
       </c>
       <c r="O13">
-        <v>3.7768145</v>
+        <v>3.7185732</v>
       </c>
       <c r="P13">
-        <v>15.107258</v>
+        <v>14.8742928</v>
       </c>
       <c r="Q13">
-        <v>-6.492742</v>
+        <v>-6.7257072</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07162072276032602</v>
+        <v>0.07186073691500465</v>
       </c>
       <c r="T13">
-        <v>0.4898095694160302</v>
+        <v>0.4943625492395665</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.953084167379285</v>
+        <v>7.182919018573832</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2379,22 +2379,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06845024848520409</v>
+        <v>0.06837965371371801</v>
       </c>
       <c r="C14">
-        <v>395.8671155301375</v>
+        <v>391.9748736849025</v>
       </c>
       <c r="D14">
-        <v>425.8471155301375</v>
+        <v>426.5698736849025</v>
       </c>
       <c r="E14">
-        <v>-187.42</v>
+        <v>-182.805</v>
       </c>
       <c r="F14">
-        <v>55.38</v>
+        <v>59.995</v>
       </c>
       <c r="G14">
         <v>25.4</v>
@@ -2415,28 +2415,28 @@
         <v>21.6</v>
       </c>
       <c r="M14">
-        <v>3.007134</v>
+        <v>3.2577285</v>
       </c>
       <c r="N14">
-        <v>18.592866</v>
+        <v>18.3422715</v>
       </c>
       <c r="O14">
-        <v>3.7185732</v>
+        <v>3.668454300000001</v>
       </c>
       <c r="P14">
-        <v>14.8742928</v>
+        <v>14.6738172</v>
       </c>
       <c r="Q14">
-        <v>-6.7257072</v>
+        <v>-6.926182799999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07186073691500465</v>
+        <v>0.07210626863645749</v>
       </c>
       <c r="T14">
-        <v>0.4943625492395665</v>
+        <v>0.4990201952659426</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.182919018573832</v>
+        <v>6.630386786375845</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2461,22 +2461,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06837965371371801</v>
+        <v>0.06830905894223195</v>
       </c>
       <c r="C15">
-        <v>391.9748736849025</v>
+        <v>388.0850893763444</v>
       </c>
       <c r="D15">
-        <v>426.5698736849025</v>
+        <v>427.2950893763444</v>
       </c>
       <c r="E15">
-        <v>-182.805</v>
+        <v>-178.19</v>
       </c>
       <c r="F15">
-        <v>59.995</v>
+        <v>64.61</v>
       </c>
       <c r="G15">
         <v>25.4</v>
@@ -2497,28 +2497,28 @@
         <v>21.6</v>
       </c>
       <c r="M15">
-        <v>3.2577285</v>
+        <v>3.508323</v>
       </c>
       <c r="N15">
-        <v>18.3422715</v>
+        <v>18.091677</v>
       </c>
       <c r="O15">
-        <v>3.668454300000001</v>
+        <v>3.6183354</v>
       </c>
       <c r="P15">
-        <v>14.6738172</v>
+        <v>14.4733416</v>
       </c>
       <c r="Q15">
-        <v>-6.926182799999999</v>
+        <v>-7.1266584</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07210626863645749</v>
+        <v>0.07235751039794412</v>
       </c>
       <c r="T15">
-        <v>0.4990201952659426</v>
+        <v>0.5037861586417695</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.630386786375845</v>
+        <v>6.156787730206141</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06830905894223195</v>
+        <v>0.06835846417074587</v>
       </c>
       <c r="C16">
-        <v>388.0850893763444</v>
+        <v>382.9622938517996</v>
       </c>
       <c r="D16">
-        <v>427.2950893763444</v>
+        <v>426.7872938517996</v>
       </c>
       <c r="E16">
-        <v>-178.19</v>
+        <v>-173.575</v>
       </c>
       <c r="F16">
-        <v>64.61</v>
+        <v>69.22500000000001</v>
       </c>
       <c r="G16">
         <v>25.4</v>
@@ -2579,45 +2579,45 @@
         <v>21.6</v>
       </c>
       <c r="M16">
-        <v>3.508323</v>
+        <v>3.828142500000001</v>
       </c>
       <c r="N16">
-        <v>18.091677</v>
+        <v>17.7718575</v>
       </c>
       <c r="O16">
-        <v>3.6183354</v>
+        <v>3.5543715</v>
       </c>
       <c r="P16">
-        <v>14.4733416</v>
+        <v>14.217486</v>
       </c>
       <c r="Q16">
-        <v>-7.1266584</v>
+        <v>-7.382514000000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07235751039794412</v>
+        <v>0.07261466373028926</v>
       </c>
       <c r="T16">
-        <v>0.5037861586417695</v>
+        <v>0.5086642623323215</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.156787730206141</v>
+        <v>5.642423185657273</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2625,22 +2625,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06835846417074587</v>
+        <v>0.0682958693992598</v>
       </c>
       <c r="C17">
-        <v>382.9622938517996</v>
+        <v>378.9908582124839</v>
       </c>
       <c r="D17">
-        <v>426.7872938517996</v>
+        <v>427.4308582124839</v>
       </c>
       <c r="E17">
-        <v>-173.575</v>
+        <v>-168.96</v>
       </c>
       <c r="F17">
-        <v>69.22499999999999</v>
+        <v>73.84</v>
       </c>
       <c r="G17">
         <v>25.4</v>
@@ -2661,28 +2661,28 @@
         <v>21.6</v>
       </c>
       <c r="M17">
-        <v>3.8281425</v>
+        <v>4.083352000000001</v>
       </c>
       <c r="N17">
-        <v>17.7718575</v>
+        <v>17.516648</v>
       </c>
       <c r="O17">
-        <v>3.554371500000001</v>
+        <v>3.5033296</v>
       </c>
       <c r="P17">
-        <v>14.217486</v>
+        <v>14.0133184</v>
       </c>
       <c r="Q17">
-        <v>-7.382513999999999</v>
+        <v>-7.586681600000002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07261466373028926</v>
+        <v>0.07287793976102357</v>
       </c>
       <c r="T17">
-        <v>0.5086642623323215</v>
+        <v>0.5136585113488391</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.642423185657274</v>
+        <v>5.289771736553694</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2707,22 +2707,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0682958693992598</v>
+        <v>0.06823327462777372</v>
       </c>
       <c r="C18">
-        <v>378.9908582124839</v>
+        <v>375.0213664013074</v>
       </c>
       <c r="D18">
-        <v>427.4308582124839</v>
+        <v>428.0763664013074</v>
       </c>
       <c r="E18">
-        <v>-168.96</v>
+        <v>-164.345</v>
       </c>
       <c r="F18">
-        <v>73.84</v>
+        <v>78.45500000000001</v>
       </c>
       <c r="G18">
         <v>25.4</v>
@@ -2743,28 +2743,28 @@
         <v>21.6</v>
       </c>
       <c r="M18">
-        <v>4.083352000000001</v>
+        <v>4.338561500000001</v>
       </c>
       <c r="N18">
-        <v>17.516648</v>
+        <v>17.2614385</v>
       </c>
       <c r="O18">
-        <v>3.5033296</v>
+        <v>3.4522877</v>
       </c>
       <c r="P18">
-        <v>14.0133184</v>
+        <v>13.8091508</v>
       </c>
       <c r="Q18">
-        <v>-7.586681600000002</v>
+        <v>-7.7908492</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07287793976102357</v>
+        <v>0.07314755979249846</v>
       </c>
       <c r="T18">
-        <v>0.5136585113488391</v>
+        <v>0.5187731037151524</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.289771736553694</v>
+        <v>4.978608693227006</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06823327462777372</v>
+        <v>0.06817067985628765</v>
       </c>
       <c r="C19">
-        <v>375.0213664013074</v>
+        <v>371.0538272383265</v>
       </c>
       <c r="D19">
-        <v>428.0763664013074</v>
+        <v>428.7238272383265</v>
       </c>
       <c r="E19">
-        <v>-164.345</v>
+        <v>-159.73</v>
       </c>
       <c r="F19">
-        <v>78.45500000000001</v>
+        <v>83.07000000000001</v>
       </c>
       <c r="G19">
         <v>25.4</v>
@@ -2825,28 +2825,28 @@
         <v>21.6</v>
       </c>
       <c r="M19">
-        <v>4.338561500000001</v>
+        <v>4.593771</v>
       </c>
       <c r="N19">
-        <v>17.2614385</v>
+        <v>17.006229</v>
       </c>
       <c r="O19">
-        <v>3.4522877</v>
+        <v>3.4012458</v>
       </c>
       <c r="P19">
-        <v>13.8091508</v>
+        <v>13.6049832</v>
       </c>
       <c r="Q19">
-        <v>-7.7908492</v>
+        <v>-7.9950168</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07314755979249846</v>
+        <v>0.07342375592230202</v>
       </c>
       <c r="T19">
-        <v>0.5187731037151524</v>
+        <v>0.5240124422367417</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.978608693227006</v>
+        <v>4.702019321381061</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2871,22 +2871,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06817067985628765</v>
+        <v>0.06848808508480159</v>
       </c>
       <c r="C20">
-        <v>371.0538272383265</v>
+        <v>363.1757468799993</v>
       </c>
       <c r="D20">
-        <v>428.7238272383265</v>
+        <v>425.4607468799994</v>
       </c>
       <c r="E20">
-        <v>-159.73</v>
+        <v>-155.115</v>
       </c>
       <c r="F20">
-        <v>83.06999999999999</v>
+        <v>87.685</v>
       </c>
       <c r="G20">
         <v>25.4</v>
@@ -2907,45 +2907,45 @@
         <v>21.6</v>
       </c>
       <c r="M20">
-        <v>4.593770999999999</v>
+        <v>5.068193000000001</v>
       </c>
       <c r="N20">
-        <v>17.006229</v>
+        <v>16.531807</v>
       </c>
       <c r="O20">
-        <v>3.4012458</v>
+        <v>3.3063614</v>
       </c>
       <c r="P20">
-        <v>13.6049832</v>
+        <v>13.2254456</v>
       </c>
       <c r="Q20">
-        <v>-7.9950168</v>
+        <v>-8.374554400000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07342375592230201</v>
+        <v>0.07370677170963158</v>
       </c>
       <c r="T20">
-        <v>0.5240124422367416</v>
+        <v>0.5293811471415799</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.702019321381062</v>
+        <v>4.261874005192777</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2953,22 +2953,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06848808508480159</v>
+        <v>0.0684454903133155</v>
       </c>
       <c r="C21">
-        <v>363.1757468799993</v>
+        <v>358.9957533074342</v>
       </c>
       <c r="D21">
-        <v>425.4607468799994</v>
+        <v>425.8957533074342</v>
       </c>
       <c r="E21">
-        <v>-155.115</v>
+        <v>-150.5</v>
       </c>
       <c r="F21">
-        <v>87.685</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="G21">
         <v>25.4</v>
@@ -2989,28 +2989,28 @@
         <v>21.6</v>
       </c>
       <c r="M21">
-        <v>5.068193000000001</v>
+        <v>5.334940000000001</v>
       </c>
       <c r="N21">
-        <v>16.531807</v>
+        <v>16.26506</v>
       </c>
       <c r="O21">
-        <v>3.3063614</v>
+        <v>3.253012</v>
       </c>
       <c r="P21">
-        <v>13.2254456</v>
+        <v>13.012048</v>
       </c>
       <c r="Q21">
-        <v>-8.374554400000001</v>
+        <v>-8.587952000000003</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07370677170963158</v>
+        <v>0.07399686289164437</v>
       </c>
       <c r="T21">
-        <v>0.5293811471415799</v>
+        <v>0.5348840696690391</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.261874005192777</v>
+        <v>4.048780304933137</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3035,22 +3035,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0684454903133155</v>
+        <v>0.06899089554182943</v>
       </c>
       <c r="C22">
-        <v>358.9957533074342</v>
+        <v>348.8770667543525</v>
       </c>
       <c r="D22">
-        <v>425.8957533074342</v>
+        <v>420.3920667543525</v>
       </c>
       <c r="E22">
-        <v>-150.5</v>
+        <v>-145.885</v>
       </c>
       <c r="F22">
-        <v>92.30000000000001</v>
+        <v>96.91500000000001</v>
       </c>
       <c r="G22">
         <v>25.4</v>
@@ -3071,45 +3071,45 @@
         <v>21.6</v>
       </c>
       <c r="M22">
-        <v>5.334940000000001</v>
+        <v>5.940889500000001</v>
       </c>
       <c r="N22">
-        <v>16.26506</v>
+        <v>15.6591105</v>
       </c>
       <c r="O22">
-        <v>3.253012</v>
+        <v>3.1318221</v>
       </c>
       <c r="P22">
-        <v>13.012048</v>
+        <v>12.5272884</v>
       </c>
       <c r="Q22">
-        <v>-8.587952000000003</v>
+        <v>-9.072711600000002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07399686289164437</v>
+        <v>0.07429429815421446</v>
       </c>
       <c r="T22">
-        <v>0.5348840696690391</v>
+        <v>0.5405263066908644</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.048780304933137</v>
+        <v>3.63581918162255</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3117,22 +3117,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06899089554182943</v>
+        <v>0.06946910077034335</v>
       </c>
       <c r="C23">
-        <v>348.8770667543525</v>
+        <v>339.5522191667652</v>
       </c>
       <c r="D23">
-        <v>420.3920667543525</v>
+        <v>415.6822191667652</v>
       </c>
       <c r="E23">
-        <v>-145.885</v>
+        <v>-141.27</v>
       </c>
       <c r="F23">
-        <v>96.91499999999999</v>
+        <v>101.53</v>
       </c>
       <c r="G23">
         <v>25.4</v>
@@ -3153,45 +3153,45 @@
         <v>21.6</v>
       </c>
       <c r="M23">
-        <v>5.9408895</v>
+        <v>6.508073</v>
       </c>
       <c r="N23">
-        <v>15.6591105</v>
+        <v>15.091927</v>
       </c>
       <c r="O23">
-        <v>3.1318221</v>
+        <v>3.018385400000001</v>
       </c>
       <c r="P23">
-        <v>12.5272884</v>
+        <v>12.0735416</v>
       </c>
       <c r="Q23">
-        <v>-9.072711600000002</v>
+        <v>-9.526458399999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07429429815421446</v>
+        <v>0.07459935996197865</v>
       </c>
       <c r="T23">
-        <v>0.5405263066908644</v>
+        <v>0.5463132164568392</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.63581918162255</v>
+        <v>3.318954781238625</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06946910077034335</v>
+        <v>0.06947690599885728</v>
       </c>
       <c r="C24">
-        <v>339.5522191667652</v>
+        <v>334.8612205508465</v>
       </c>
       <c r="D24">
-        <v>415.6822191667652</v>
+        <v>415.6062205508465</v>
       </c>
       <c r="E24">
-        <v>-141.27</v>
+        <v>-136.655</v>
       </c>
       <c r="F24">
-        <v>101.53</v>
+        <v>106.145</v>
       </c>
       <c r="G24">
         <v>25.4</v>
@@ -3235,28 +3235,28 @@
         <v>21.6</v>
       </c>
       <c r="M24">
-        <v>6.508073</v>
+        <v>6.803894500000001</v>
       </c>
       <c r="N24">
-        <v>15.091927</v>
+        <v>14.7961055</v>
       </c>
       <c r="O24">
-        <v>3.018385400000001</v>
+        <v>2.9592211</v>
       </c>
       <c r="P24">
-        <v>12.0735416</v>
+        <v>11.8368844</v>
       </c>
       <c r="Q24">
-        <v>-9.526458399999999</v>
+        <v>-9.763115600000003</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07459935996197865</v>
+        <v>0.0749123454530614</v>
       </c>
       <c r="T24">
-        <v>0.5463132164568392</v>
+        <v>0.5522504355673846</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.318954781238625</v>
+        <v>3.174652399445641</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3281,22 +3281,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06947690599885728</v>
+        <v>0.06948471122737121</v>
       </c>
       <c r="C25">
-        <v>334.8612205508465</v>
+        <v>330.1702497192956</v>
       </c>
       <c r="D25">
-        <v>415.6062205508465</v>
+        <v>415.5302497192956</v>
       </c>
       <c r="E25">
-        <v>-136.655</v>
+        <v>-132.04</v>
       </c>
       <c r="F25">
-        <v>106.145</v>
+        <v>110.76</v>
       </c>
       <c r="G25">
         <v>25.4</v>
@@ -3317,28 +3317,28 @@
         <v>21.6</v>
       </c>
       <c r="M25">
-        <v>6.803894500000001</v>
+        <v>7.099716000000001</v>
       </c>
       <c r="N25">
-        <v>14.7961055</v>
+        <v>14.500284</v>
       </c>
       <c r="O25">
-        <v>2.9592211</v>
+        <v>2.9000568</v>
       </c>
       <c r="P25">
-        <v>11.8368844</v>
+        <v>11.6002272</v>
       </c>
       <c r="Q25">
-        <v>-9.763115600000003</v>
+        <v>-9.999772800000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0749123454530614</v>
+        <v>0.07523356740443579</v>
       </c>
       <c r="T25">
-        <v>0.5522504355673846</v>
+        <v>0.5583438972861023</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.174652399445641</v>
+        <v>3.042375216135406</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3363,22 +3363,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06948471122737121</v>
+        <v>0.07105251645588513</v>
       </c>
       <c r="C26">
-        <v>330.1702497192956</v>
+        <v>310.8384423548295</v>
       </c>
       <c r="D26">
-        <v>415.5302497192956</v>
+        <v>400.8134423548295</v>
       </c>
       <c r="E26">
-        <v>-132.04</v>
+        <v>-127.425</v>
       </c>
       <c r="F26">
-        <v>110.76</v>
+        <v>115.375</v>
       </c>
       <c r="G26">
         <v>25.4</v>
@@ -3399,45 +3399,45 @@
         <v>21.6</v>
       </c>
       <c r="M26">
-        <v>7.099716</v>
+        <v>8.295462500000001</v>
       </c>
       <c r="N26">
-        <v>14.500284</v>
+        <v>13.3045375</v>
       </c>
       <c r="O26">
-        <v>2.9000568</v>
+        <v>2.6609075</v>
       </c>
       <c r="P26">
-        <v>11.6002272</v>
+        <v>10.64363</v>
       </c>
       <c r="Q26">
-        <v>-9.999772800000001</v>
+        <v>-10.95637</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07523356740443579</v>
+        <v>0.07556335527451351</v>
       </c>
       <c r="T26">
-        <v>0.5583438972861022</v>
+        <v>0.564599851317319</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.042375216135406</v>
+        <v>2.603833119612077</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3445,22 +3445,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07105251645588513</v>
+        <v>0.07112272168439907</v>
       </c>
       <c r="C27">
-        <v>310.8384423548295</v>
+        <v>305.5887805454385</v>
       </c>
       <c r="D27">
-        <v>400.8134423548295</v>
+        <v>400.1787805454385</v>
       </c>
       <c r="E27">
-        <v>-127.425</v>
+        <v>-122.81</v>
       </c>
       <c r="F27">
-        <v>115.375</v>
+        <v>119.99</v>
       </c>
       <c r="G27">
         <v>25.4</v>
@@ -3481,28 +3481,28 @@
         <v>21.6</v>
       </c>
       <c r="M27">
-        <v>8.295462500000001</v>
+        <v>8.627281000000002</v>
       </c>
       <c r="N27">
-        <v>13.3045375</v>
+        <v>12.972719</v>
       </c>
       <c r="O27">
-        <v>2.6609075</v>
+        <v>2.5945438</v>
       </c>
       <c r="P27">
-        <v>10.64363</v>
+        <v>10.3781752</v>
       </c>
       <c r="Q27">
-        <v>-10.95637</v>
+        <v>-11.2218248</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07556335527451351</v>
+        <v>0.075902056330269</v>
       </c>
       <c r="T27">
-        <v>0.564599851317319</v>
+        <v>0.5710248851872175</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.603833119612077</v>
+        <v>2.503685691934689</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3527,22 +3527,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07112272168439907</v>
+        <v>0.07203532691291299</v>
       </c>
       <c r="C28">
-        <v>305.5887805454385</v>
+        <v>292.9029317680063</v>
       </c>
       <c r="D28">
-        <v>400.1787805454385</v>
+        <v>392.1079317680064</v>
       </c>
       <c r="E28">
-        <v>-122.81</v>
+        <v>-118.195</v>
       </c>
       <c r="F28">
-        <v>119.99</v>
+        <v>124.605</v>
       </c>
       <c r="G28">
         <v>25.4</v>
@@ -3563,45 +3563,45 @@
         <v>21.6</v>
       </c>
       <c r="M28">
-        <v>8.627281000000002</v>
+        <v>9.445059000000001</v>
       </c>
       <c r="N28">
-        <v>12.972719</v>
+        <v>12.154941</v>
       </c>
       <c r="O28">
-        <v>2.5945438</v>
+        <v>2.4309882</v>
       </c>
       <c r="P28">
-        <v>10.3781752</v>
+        <v>9.723952800000001</v>
       </c>
       <c r="Q28">
-        <v>-11.2218248</v>
+        <v>-11.8760472</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.075902056330269</v>
+        <v>0.07625003686700409</v>
       </c>
       <c r="T28">
-        <v>0.5710248851872175</v>
+        <v>0.5776259473823185</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.503685691934689</v>
+        <v>2.286910012949628</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3609,22 +3609,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07203532691291299</v>
+        <v>0.07213673214142691</v>
       </c>
       <c r="C29">
-        <v>292.9029317680063</v>
+        <v>287.4111812927243</v>
       </c>
       <c r="D29">
-        <v>392.1079317680064</v>
+        <v>391.2311812927244</v>
       </c>
       <c r="E29">
-        <v>-118.195</v>
+        <v>-113.58</v>
       </c>
       <c r="F29">
-        <v>124.605</v>
+        <v>129.22</v>
       </c>
       <c r="G29">
         <v>25.4</v>
@@ -3645,28 +3645,28 @@
         <v>21.6</v>
       </c>
       <c r="M29">
-        <v>9.445059000000001</v>
+        <v>9.794876</v>
       </c>
       <c r="N29">
-        <v>12.154941</v>
+        <v>11.805124</v>
       </c>
       <c r="O29">
-        <v>2.4309882</v>
+        <v>2.3610248</v>
       </c>
       <c r="P29">
-        <v>9.723952800000001</v>
+        <v>9.4440992</v>
       </c>
       <c r="Q29">
-        <v>-11.8760472</v>
+        <v>-12.1559008</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07625003686700409</v>
+        <v>0.07660768352975959</v>
       </c>
       <c r="T29">
-        <v>0.5776259473823185</v>
+        <v>0.5844103724161724</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.286910012949628</v>
+        <v>2.205234655344284</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3691,22 +3691,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07213673214142691</v>
+        <v>0.07223813736994084</v>
       </c>
       <c r="C30">
-        <v>287.4111812927243</v>
+        <v>281.9233428854218</v>
       </c>
       <c r="D30">
-        <v>391.2311812927244</v>
+        <v>390.3583428854218</v>
       </c>
       <c r="E30">
-        <v>-113.58</v>
+        <v>-108.965</v>
       </c>
       <c r="F30">
-        <v>129.22</v>
+        <v>133.835</v>
       </c>
       <c r="G30">
         <v>25.4</v>
@@ -3727,28 +3727,28 @@
         <v>21.6</v>
       </c>
       <c r="M30">
-        <v>9.794876</v>
+        <v>10.144693</v>
       </c>
       <c r="N30">
-        <v>11.805124</v>
+        <v>11.455307</v>
       </c>
       <c r="O30">
-        <v>2.3610248</v>
+        <v>2.2910614</v>
       </c>
       <c r="P30">
-        <v>9.4440992</v>
+        <v>9.164245599999999</v>
       </c>
       <c r="Q30">
-        <v>-12.1559008</v>
+        <v>-12.4357544</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07660768352975959</v>
+        <v>0.07697540474639554</v>
       </c>
       <c r="T30">
-        <v>0.5844103724161724</v>
+        <v>0.5913859080143602</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.205234655344284</v>
+        <v>2.129192081022067</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3773,22 +3773,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07223813736994084</v>
+        <v>0.07233954259845476</v>
       </c>
       <c r="C31">
-        <v>281.9233428854218</v>
+        <v>276.4393904208639</v>
       </c>
       <c r="D31">
-        <v>390.3583428854218</v>
+        <v>389.4893904208639</v>
       </c>
       <c r="E31">
-        <v>-108.965</v>
+        <v>-104.35</v>
       </c>
       <c r="F31">
-        <v>133.835</v>
+        <v>138.45</v>
       </c>
       <c r="G31">
         <v>25.4</v>
@@ -3809,28 +3809,28 @@
         <v>21.6</v>
       </c>
       <c r="M31">
-        <v>10.144693</v>
+        <v>10.49451</v>
       </c>
       <c r="N31">
-        <v>11.455307</v>
+        <v>11.10549</v>
       </c>
       <c r="O31">
-        <v>2.291061400000001</v>
+        <v>2.221098</v>
       </c>
       <c r="P31">
-        <v>9.164245600000003</v>
+        <v>8.884392000000002</v>
       </c>
       <c r="Q31">
-        <v>-12.4357544</v>
+        <v>-12.715608</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07697540474639554</v>
+        <v>0.07735363228350681</v>
       </c>
       <c r="T31">
-        <v>0.5913859080143602</v>
+        <v>0.598560744629639</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.129192081022068</v>
+        <v>2.058219011654665</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07233954259845476</v>
+        <v>0.07596254782696868</v>
       </c>
       <c r="C32">
-        <v>276.4393904208639</v>
+        <v>243.1297139583626</v>
       </c>
       <c r="D32">
-        <v>389.4893904208639</v>
+        <v>360.7947139583626</v>
       </c>
       <c r="E32">
-        <v>-104.35</v>
+        <v>-99.73499999999999</v>
       </c>
       <c r="F32">
-        <v>138.45</v>
+        <v>143.065</v>
       </c>
       <c r="G32">
         <v>25.4</v>
@@ -3891,45 +3891,45 @@
         <v>21.6</v>
       </c>
       <c r="M32">
-        <v>10.49451</v>
+        <v>12.87585</v>
       </c>
       <c r="N32">
-        <v>11.10549</v>
+        <v>8.724150000000002</v>
       </c>
       <c r="O32">
-        <v>2.221098</v>
+        <v>1.74483</v>
       </c>
       <c r="P32">
-        <v>8.884392000000002</v>
+        <v>6.979320000000001</v>
       </c>
       <c r="Q32">
-        <v>-12.715608</v>
+        <v>-14.62068</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07735363228350681</v>
+        <v>0.07774282293763578</v>
       </c>
       <c r="T32">
-        <v>0.598560744629639</v>
+        <v>0.6059435475236217</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.058219011654665</v>
+        <v>1.677559151434663</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3937,22 +3937,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07596254782696868</v>
+        <v>0.0761775530554826</v>
       </c>
       <c r="C33">
-        <v>243.1297139583626</v>
+        <v>236.9441656280597</v>
       </c>
       <c r="D33">
-        <v>360.7947139583626</v>
+        <v>359.2241656280598</v>
       </c>
       <c r="E33">
-        <v>-99.73499999999999</v>
+        <v>-95.11999999999998</v>
       </c>
       <c r="F33">
-        <v>143.065</v>
+        <v>147.68</v>
       </c>
       <c r="G33">
         <v>25.4</v>
@@ -3973,28 +3973,28 @@
         <v>21.6</v>
       </c>
       <c r="M33">
-        <v>12.87585</v>
+        <v>13.2912</v>
       </c>
       <c r="N33">
-        <v>8.724150000000002</v>
+        <v>8.308800000000002</v>
       </c>
       <c r="O33">
-        <v>1.74483</v>
+        <v>1.66176</v>
       </c>
       <c r="P33">
-        <v>6.979320000000001</v>
+        <v>6.647040000000001</v>
       </c>
       <c r="Q33">
-        <v>-14.62068</v>
+        <v>-14.95296</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07774282293763578</v>
+        <v>0.07814346037570973</v>
       </c>
       <c r="T33">
-        <v>0.6059435475236217</v>
+        <v>0.613543491679192</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.677559151434663</v>
+        <v>1.625135427952329</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4019,22 +4019,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0761775530554826</v>
+        <v>0.07639255828399653</v>
       </c>
       <c r="C34">
-        <v>236.9441656280597</v>
+        <v>230.7722313072358</v>
       </c>
       <c r="D34">
-        <v>359.2241656280598</v>
+        <v>357.6672313072359</v>
       </c>
       <c r="E34">
-        <v>-95.11999999999998</v>
+        <v>-90.50499999999997</v>
       </c>
       <c r="F34">
-        <v>147.68</v>
+        <v>152.295</v>
       </c>
       <c r="G34">
         <v>25.4</v>
@@ -4055,28 +4055,28 @@
         <v>21.6</v>
       </c>
       <c r="M34">
-        <v>13.2912</v>
+        <v>13.70655</v>
       </c>
       <c r="N34">
-        <v>8.308800000000002</v>
+        <v>7.89345</v>
       </c>
       <c r="O34">
-        <v>1.66176</v>
+        <v>1.57869</v>
       </c>
       <c r="P34">
-        <v>6.647040000000001</v>
+        <v>6.31476</v>
       </c>
       <c r="Q34">
-        <v>-14.95296</v>
+        <v>-15.28524</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07814346037570973</v>
+        <v>0.07855605714029334</v>
       </c>
       <c r="T34">
-        <v>0.613543491679192</v>
+        <v>0.6213702998394062</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4093,7 +4093,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.625135427952329</v>
+        <v>1.575888899832562</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4101,22 +4101,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07639255828399653</v>
+        <v>0.07660756351251045</v>
       </c>
       <c r="C35">
-        <v>230.7722313072358</v>
+        <v>224.6137347439868</v>
       </c>
       <c r="D35">
-        <v>357.6672313072359</v>
+        <v>356.1237347439869</v>
       </c>
       <c r="E35">
-        <v>-90.50499999999997</v>
+        <v>-85.88999999999996</v>
       </c>
       <c r="F35">
-        <v>152.295</v>
+        <v>156.91</v>
       </c>
       <c r="G35">
         <v>25.4</v>
@@ -4137,28 +4137,28 @@
         <v>21.6</v>
       </c>
       <c r="M35">
-        <v>13.70655</v>
+        <v>14.1219</v>
       </c>
       <c r="N35">
-        <v>7.89345</v>
+        <v>7.4781</v>
       </c>
       <c r="O35">
-        <v>1.57869</v>
+        <v>1.49562</v>
       </c>
       <c r="P35">
-        <v>6.31476</v>
+        <v>5.98248</v>
       </c>
       <c r="Q35">
-        <v>-15.28524</v>
+        <v>-15.61752</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07855605714029334</v>
+        <v>0.07898115683713706</v>
       </c>
       <c r="T35">
-        <v>0.6213702998394062</v>
+        <v>0.6294342840044753</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.575888899832562</v>
+        <v>1.529539226308075</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4183,22 +4183,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07660756351251045</v>
+        <v>0.09378828238073482</v>
       </c>
       <c r="C36">
-        <v>224.6137347439868</v>
+        <v>128.6823265282708</v>
       </c>
       <c r="D36">
-        <v>356.1237347439869</v>
+        <v>264.8073265282708</v>
       </c>
       <c r="E36">
-        <v>-85.88999999999996</v>
+        <v>-81.27499999999998</v>
       </c>
       <c r="F36">
-        <v>156.91</v>
+        <v>161.525</v>
       </c>
       <c r="G36">
         <v>25.4</v>
@@ -4219,45 +4219,45 @@
         <v>21.6</v>
       </c>
       <c r="M36">
-        <v>14.1219</v>
+        <v>23.71187</v>
       </c>
       <c r="N36">
-        <v>7.4781</v>
+        <v>-2.111870000000003</v>
       </c>
       <c r="O36">
-        <v>1.49562</v>
+        <v>-0.4223740000000007</v>
       </c>
       <c r="P36">
-        <v>5.98248</v>
+        <v>-1.689496000000003</v>
       </c>
       <c r="Q36">
-        <v>-15.61752</v>
+        <v>-23.289496</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07898115683713706</v>
+        <v>0.07964471145498497</v>
       </c>
       <c r="T36">
-        <v>0.6294342840044753</v>
+        <v>0.642021669906449</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2</v>
+        <v>0.1821872336513316</v>
       </c>
       <c r="W36">
-        <v>0.07199999999999999</v>
+        <v>0.1200549140999845</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.529539226308075</v>
+        <v>0.9109361682566578</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09378828238073482</v>
+        <v>0.0947982823807348</v>
       </c>
       <c r="C37">
-        <v>128.6823265282708</v>
+        <v>120.1349033687287</v>
       </c>
       <c r="D37">
-        <v>264.8073265282708</v>
+        <v>260.8749033687287</v>
       </c>
       <c r="E37">
-        <v>-81.27499999999998</v>
+        <v>-76.65999999999997</v>
       </c>
       <c r="F37">
-        <v>161.525</v>
+        <v>166.14</v>
       </c>
       <c r="G37">
         <v>25.4</v>
@@ -4301,37 +4301,37 @@
         <v>21.6</v>
       </c>
       <c r="M37">
-        <v>23.71187</v>
+        <v>24.38935200000001</v>
       </c>
       <c r="N37">
-        <v>-2.111870000000003</v>
+        <v>-2.789352000000004</v>
       </c>
       <c r="O37">
-        <v>-0.4223740000000007</v>
+        <v>-0.5578704000000009</v>
       </c>
       <c r="P37">
-        <v>-1.689496000000003</v>
+        <v>-2.231481600000004</v>
       </c>
       <c r="Q37">
-        <v>-23.289496</v>
+        <v>-23.8314816</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07964471145498497</v>
+        <v>0.0801735350714691</v>
       </c>
       <c r="T37">
-        <v>0.642021669906449</v>
+        <v>0.6520532584987373</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1821872336513316</v>
+        <v>0.1771264771610168</v>
       </c>
       <c r="W37">
-        <v>0.1200549140999845</v>
+        <v>0.1207978331527627</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9109361682566578</v>
+        <v>0.885632385805084</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09479828238073482</v>
+        <v>0.0958082823807348</v>
       </c>
       <c r="C38">
-        <v>120.1349033687287</v>
+        <v>111.7025651709288</v>
       </c>
       <c r="D38">
-        <v>260.8749033687287</v>
+        <v>257.0575651709289</v>
       </c>
       <c r="E38">
-        <v>-76.66</v>
+        <v>-72.04499999999999</v>
       </c>
       <c r="F38">
-        <v>166.14</v>
+        <v>170.755</v>
       </c>
       <c r="G38">
         <v>25.4</v>
@@ -4383,37 +4383,37 @@
         <v>21.6</v>
       </c>
       <c r="M38">
-        <v>24.389352</v>
+        <v>25.066834</v>
       </c>
       <c r="N38">
-        <v>-2.789351999999997</v>
+        <v>-3.466833999999999</v>
       </c>
       <c r="O38">
-        <v>-0.5578703999999995</v>
+        <v>-0.6933667999999997</v>
       </c>
       <c r="P38">
-        <v>-2.231481599999998</v>
+        <v>-2.773467199999999</v>
       </c>
       <c r="Q38">
-        <v>-23.8314816</v>
+        <v>-24.3734672</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0801735350714691</v>
+        <v>0.08071914673927021</v>
       </c>
       <c r="T38">
-        <v>0.6520532584987372</v>
+        <v>0.6624033102209395</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1771264771610168</v>
+        <v>0.172339275075584</v>
       </c>
       <c r="W38">
-        <v>0.1207978331527627</v>
+        <v>0.1215005944189043</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8856323858050842</v>
+        <v>0.8616963753779198</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0958082823807348</v>
+        <v>0.09681828238073481</v>
       </c>
       <c r="C39">
-        <v>111.7025651709288</v>
+        <v>103.3803327384518</v>
       </c>
       <c r="D39">
-        <v>257.0575651709289</v>
+        <v>253.3503327384519</v>
       </c>
       <c r="E39">
-        <v>-72.04499999999999</v>
+        <v>-67.42999999999998</v>
       </c>
       <c r="F39">
-        <v>170.755</v>
+        <v>175.37</v>
       </c>
       <c r="G39">
         <v>25.4</v>
@@ -4465,37 +4465,37 @@
         <v>21.6</v>
       </c>
       <c r="M39">
-        <v>25.066834</v>
+        <v>25.744316</v>
       </c>
       <c r="N39">
-        <v>-3.466833999999999</v>
+        <v>-4.144316000000003</v>
       </c>
       <c r="O39">
-        <v>-0.6933667999999997</v>
+        <v>-0.8288632000000007</v>
       </c>
       <c r="P39">
-        <v>-2.773467199999999</v>
+        <v>-3.315452800000003</v>
       </c>
       <c r="Q39">
-        <v>-24.3734672</v>
+        <v>-24.9154528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08071914673927021</v>
+        <v>0.08128235878345198</v>
       </c>
       <c r="T39">
-        <v>0.6624033102209395</v>
+        <v>0.6730872345793417</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.172339275075584</v>
+        <v>0.1678040309946475</v>
       </c>
       <c r="W39">
-        <v>0.1215005944189043</v>
+        <v>0.1221663682499858</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8616963753779198</v>
+        <v>0.8390201549732375</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4511,22 +4511,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09681828238073481</v>
+        <v>0.09782828238073482</v>
       </c>
       <c r="C40">
-        <v>103.3803327384518</v>
+        <v>95.16351002718511</v>
       </c>
       <c r="D40">
-        <v>253.3503327384519</v>
+        <v>249.7485100271851</v>
       </c>
       <c r="E40">
-        <v>-67.42999999999998</v>
+        <v>-62.81499999999997</v>
       </c>
       <c r="F40">
-        <v>175.37</v>
+        <v>179.985</v>
       </c>
       <c r="G40">
         <v>25.4</v>
@@ -4547,37 +4547,37 @@
         <v>21.6</v>
       </c>
       <c r="M40">
-        <v>25.744316</v>
+        <v>26.42179800000001</v>
       </c>
       <c r="N40">
-        <v>-4.144316000000003</v>
+        <v>-4.821798000000005</v>
       </c>
       <c r="O40">
-        <v>-0.8288632000000007</v>
+        <v>-0.964359600000001</v>
       </c>
       <c r="P40">
-        <v>-3.315452800000003</v>
+        <v>-3.857438400000004</v>
       </c>
       <c r="Q40">
-        <v>-24.9154528</v>
+        <v>-25.4574384</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08128235878345198</v>
+        <v>0.08186403679629546</v>
       </c>
       <c r="T40">
-        <v>0.6730872345793417</v>
+        <v>0.6841214515396589</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1678040309946475</v>
+        <v>0.1635013635332463</v>
       </c>
       <c r="W40">
-        <v>0.1221663682499858</v>
+        <v>0.1227979998333195</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8390201549732375</v>
+        <v>0.8175068176662313</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4593,22 +4593,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09782828238073482</v>
+        <v>0.1208412179288126</v>
       </c>
       <c r="C41">
-        <v>95.16351002718511</v>
+        <v>29.44174364302347</v>
       </c>
       <c r="D41">
-        <v>249.7485100271851</v>
+        <v>188.6417436430235</v>
       </c>
       <c r="E41">
-        <v>-62.81499999999997</v>
+        <v>-58.19999999999996</v>
       </c>
       <c r="F41">
-        <v>179.985</v>
+        <v>184.6</v>
       </c>
       <c r="G41">
         <v>25.4</v>
@@ -4629,45 +4629,45 @@
         <v>21.6</v>
       </c>
       <c r="M41">
-        <v>26.42179800000001</v>
+        <v>37.06768</v>
       </c>
       <c r="N41">
-        <v>-4.821798000000005</v>
+        <v>-15.46768</v>
       </c>
       <c r="O41">
-        <v>-0.964359600000001</v>
+        <v>-3.093536</v>
       </c>
       <c r="P41">
-        <v>-3.857438400000004</v>
+        <v>-12.374144</v>
       </c>
       <c r="Q41">
-        <v>-25.4574384</v>
+        <v>-33.974144</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08186403679629546</v>
+        <v>0.08313666332303007</v>
       </c>
       <c r="T41">
-        <v>0.6841214515396589</v>
+        <v>0.7082627064872189</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1635013635332463</v>
+        <v>0.1165435765065416</v>
       </c>
       <c r="W41">
-        <v>0.1227979998333195</v>
+        <v>0.1773980498374865</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8175068176662313</v>
+        <v>0.5827178825327077</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1208412179288126</v>
+        <v>0.1223912179288126</v>
       </c>
       <c r="C42">
-        <v>29.44174364302347</v>
+        <v>21.7684074931409</v>
       </c>
       <c r="D42">
-        <v>188.6417436430235</v>
+        <v>185.5834074931409</v>
       </c>
       <c r="E42">
-        <v>-58.19999999999996</v>
+        <v>-53.58499999999998</v>
       </c>
       <c r="F42">
-        <v>184.6</v>
+        <v>189.215</v>
       </c>
       <c r="G42">
         <v>25.4</v>
@@ -4711,37 +4711,37 @@
         <v>21.6</v>
       </c>
       <c r="M42">
-        <v>37.06768</v>
+        <v>37.994372</v>
       </c>
       <c r="N42">
-        <v>-15.46768</v>
+        <v>-16.394372</v>
       </c>
       <c r="O42">
-        <v>-3.093536</v>
+        <v>-3.278874399999999</v>
       </c>
       <c r="P42">
-        <v>-12.374144</v>
+        <v>-13.1154976</v>
       </c>
       <c r="Q42">
-        <v>-33.974144</v>
+        <v>-34.7154976</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08313666332303007</v>
+        <v>0.08376948812511531</v>
       </c>
       <c r="T42">
-        <v>0.7082627064872189</v>
+        <v>0.7202671591395445</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1165435765065416</v>
+        <v>0.1137010502502845</v>
       </c>
       <c r="W42">
-        <v>0.1773980498374865</v>
+        <v>0.1779688291097429</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5827178825327077</v>
+        <v>0.5685052512514223</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4757,22 +4757,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1223912179288126</v>
+        <v>0.1239412179288126</v>
       </c>
       <c r="C43">
-        <v>21.7684074931409</v>
+        <v>14.19265523592838</v>
       </c>
       <c r="D43">
-        <v>185.5834074931409</v>
+        <v>182.6226552359284</v>
       </c>
       <c r="E43">
-        <v>-53.58499999999998</v>
+        <v>-48.96999999999997</v>
       </c>
       <c r="F43">
-        <v>189.215</v>
+        <v>193.83</v>
       </c>
       <c r="G43">
         <v>25.4</v>
@@ -4793,37 +4793,37 @@
         <v>21.6</v>
       </c>
       <c r="M43">
-        <v>37.994372</v>
+        <v>38.921064</v>
       </c>
       <c r="N43">
-        <v>-16.394372</v>
+        <v>-17.321064</v>
       </c>
       <c r="O43">
-        <v>-3.278874399999999</v>
+        <v>-3.4642128</v>
       </c>
       <c r="P43">
-        <v>-13.1154976</v>
+        <v>-13.8568512</v>
       </c>
       <c r="Q43">
-        <v>-34.7154976</v>
+        <v>-35.4568512</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08376948812511531</v>
+        <v>0.08442413447210007</v>
       </c>
       <c r="T43">
-        <v>0.7202671591395445</v>
+        <v>0.732685558435054</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1137010502502845</v>
+        <v>0.1109938823871824</v>
       </c>
       <c r="W43">
-        <v>0.1779688291097429</v>
+        <v>0.1785124284166538</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5685052512514223</v>
+        <v>0.5549694119359121</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4839,22 +4839,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1239412179288126</v>
+        <v>0.1254912179288126</v>
       </c>
       <c r="C44">
-        <v>14.19265523592841</v>
+        <v>6.70988972452858</v>
       </c>
       <c r="D44">
-        <v>182.6226552359284</v>
+        <v>179.7548897245286</v>
       </c>
       <c r="E44">
-        <v>-48.97</v>
+        <v>-44.35499999999999</v>
       </c>
       <c r="F44">
-        <v>193.83</v>
+        <v>198.445</v>
       </c>
       <c r="G44">
         <v>25.4</v>
@@ -4875,37 +4875,37 @@
         <v>21.6</v>
       </c>
       <c r="M44">
-        <v>38.921064</v>
+        <v>39.847756</v>
       </c>
       <c r="N44">
-        <v>-17.321064</v>
+        <v>-18.247756</v>
       </c>
       <c r="O44">
-        <v>-3.4642128</v>
+        <v>-3.649551199999999</v>
       </c>
       <c r="P44">
-        <v>-13.8568512</v>
+        <v>-14.5982048</v>
       </c>
       <c r="Q44">
-        <v>-35.4568512</v>
+        <v>-36.1982048</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08442413447210007</v>
+        <v>0.08510175086634743</v>
       </c>
       <c r="T44">
-        <v>0.7326855584350539</v>
+        <v>0.7455396910391776</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1109938823871824</v>
+        <v>0.1084126293084108</v>
       </c>
       <c r="W44">
-        <v>0.1785124284166538</v>
+        <v>0.1790307440348711</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5549694119359121</v>
+        <v>0.5420631465420538</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1254912179288126</v>
+        <v>0.1270412179288126</v>
       </c>
       <c r="C45">
-        <v>6.70988972452858</v>
+        <v>-0.6842018920658859</v>
       </c>
       <c r="D45">
-        <v>179.7548897245286</v>
+        <v>176.9757981079341</v>
       </c>
       <c r="E45">
-        <v>-44.35499999999999</v>
+        <v>-39.73999999999998</v>
       </c>
       <c r="F45">
-        <v>198.445</v>
+        <v>203.06</v>
       </c>
       <c r="G45">
         <v>25.4</v>
@@ -4957,37 +4957,37 @@
         <v>21.6</v>
       </c>
       <c r="M45">
-        <v>39.847756</v>
+        <v>40.774448</v>
       </c>
       <c r="N45">
-        <v>-18.247756</v>
+        <v>-19.174448</v>
       </c>
       <c r="O45">
-        <v>-3.649551199999999</v>
+        <v>-3.8348896</v>
       </c>
       <c r="P45">
-        <v>-14.5982048</v>
+        <v>-15.3395584</v>
       </c>
       <c r="Q45">
-        <v>-36.1982048</v>
+        <v>-36.9395584</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08510175086634743</v>
+        <v>0.08580356784610363</v>
       </c>
       <c r="T45">
-        <v>0.7455396910391776</v>
+        <v>0.7588528998077344</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1084126293084108</v>
+        <v>0.1059487059150378</v>
       </c>
       <c r="W45">
-        <v>0.1790307440348711</v>
+        <v>0.1795254998522604</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5420631465420538</v>
+        <v>0.5297435295751889</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1270412179288126</v>
+        <v>0.1285912179288126</v>
       </c>
       <c r="C46">
-        <v>-0.6842018920658859</v>
+        <v>-7.993669811125443</v>
       </c>
       <c r="D46">
-        <v>176.9757981079341</v>
+        <v>174.2813301888746</v>
       </c>
       <c r="E46">
-        <v>-39.73999999999998</v>
+        <v>-35.12499999999997</v>
       </c>
       <c r="F46">
-        <v>203.06</v>
+        <v>207.675</v>
       </c>
       <c r="G46">
         <v>25.4</v>
@@ -5039,37 +5039,37 @@
         <v>21.6</v>
       </c>
       <c r="M46">
-        <v>40.774448</v>
+        <v>41.70114</v>
       </c>
       <c r="N46">
-        <v>-19.174448</v>
+        <v>-20.10114</v>
       </c>
       <c r="O46">
-        <v>-3.8348896</v>
+        <v>-4.020228</v>
       </c>
       <c r="P46">
-        <v>-15.3395584</v>
+        <v>-16.080912</v>
       </c>
       <c r="Q46">
-        <v>-36.9395584</v>
+        <v>-37.68091200000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08580356784610363</v>
+        <v>0.08653090544330552</v>
       </c>
       <c r="T46">
-        <v>0.7588528998077344</v>
+        <v>0.7726502252587841</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1059487059150378</v>
+        <v>0.1035942902280369</v>
       </c>
       <c r="W46">
-        <v>0.1795254998522604</v>
+        <v>0.1799982665222102</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5297435295751889</v>
+        <v>0.5179714511401847</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5085,22 +5085,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1285912179288126</v>
+        <v>0.1301412179288126</v>
       </c>
       <c r="C47">
-        <v>-7.993669811125443</v>
+        <v>-15.22232127093017</v>
       </c>
       <c r="D47">
-        <v>174.2813301888746</v>
+        <v>171.6676787290698</v>
       </c>
       <c r="E47">
-        <v>-35.12499999999997</v>
+        <v>-30.50999999999996</v>
       </c>
       <c r="F47">
-        <v>207.675</v>
+        <v>212.29</v>
       </c>
       <c r="G47">
         <v>25.4</v>
@@ -5121,37 +5121,37 @@
         <v>21.6</v>
       </c>
       <c r="M47">
-        <v>41.70114</v>
+        <v>42.62783200000001</v>
       </c>
       <c r="N47">
-        <v>-20.10114</v>
+        <v>-21.027832</v>
       </c>
       <c r="O47">
-        <v>-4.020228</v>
+        <v>-4.205566400000001</v>
       </c>
       <c r="P47">
-        <v>-16.080912</v>
+        <v>-16.8222656</v>
       </c>
       <c r="Q47">
-        <v>-37.68091200000001</v>
+        <v>-38.4222656</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08653090544330552</v>
+        <v>0.0872851814700334</v>
       </c>
       <c r="T47">
-        <v>0.7726502252587841</v>
+        <v>0.7869585627635765</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1035942902280369</v>
+        <v>0.1013422404404709</v>
       </c>
       <c r="W47">
-        <v>0.1799982665222102</v>
+        <v>0.1804504781195534</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5179714511401847</v>
+        <v>0.5067112022023545</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5167,22 +5167,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1301412179288126</v>
+        <v>0.1483038072893837</v>
       </c>
       <c r="C48">
-        <v>-15.22232127093017</v>
+        <v>-45.49540753793957</v>
       </c>
       <c r="D48">
-        <v>171.6676787290698</v>
+        <v>146.0095924620604</v>
       </c>
       <c r="E48">
-        <v>-30.50999999999996</v>
+        <v>-25.89499999999998</v>
       </c>
       <c r="F48">
-        <v>212.29</v>
+        <v>216.905</v>
       </c>
       <c r="G48">
         <v>25.4</v>
@@ -5203,45 +5203,45 @@
         <v>21.6</v>
       </c>
       <c r="M48">
-        <v>42.62783200000001</v>
+        <v>51.146199</v>
       </c>
       <c r="N48">
-        <v>-21.027832</v>
+        <v>-29.546199</v>
       </c>
       <c r="O48">
-        <v>-4.205566400000001</v>
+        <v>-5.909239800000001</v>
       </c>
       <c r="P48">
-        <v>-16.8222656</v>
+        <v>-23.6369592</v>
       </c>
       <c r="Q48">
-        <v>-38.4222656</v>
+        <v>-45.2369592</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0872851814700334</v>
+        <v>0.08837469312148893</v>
       </c>
       <c r="T48">
-        <v>0.7869585627635765</v>
+        <v>0.8076261961922249</v>
       </c>
       <c r="U48">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1013422404404709</v>
+        <v>0.08446375457929924</v>
       </c>
       <c r="W48">
-        <v>0.1804504781195534</v>
+        <v>0.2158834466702013</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5067112022023545</v>
+        <v>0.4223187728964962</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5249,22 +5249,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1483038072893837</v>
+        <v>0.1502038072893837</v>
       </c>
       <c r="C49">
-        <v>-45.49540753793957</v>
+        <v>-52.35819416248881</v>
       </c>
       <c r="D49">
-        <v>146.0095924620604</v>
+        <v>143.7618058375112</v>
       </c>
       <c r="E49">
-        <v>-25.89499999999998</v>
+        <v>-21.27999999999997</v>
       </c>
       <c r="F49">
-        <v>216.905</v>
+        <v>221.52</v>
       </c>
       <c r="G49">
         <v>25.4</v>
@@ -5285,37 +5285,37 @@
         <v>21.6</v>
       </c>
       <c r="M49">
-        <v>51.146199</v>
+        <v>52.234416</v>
       </c>
       <c r="N49">
-        <v>-29.546199</v>
+        <v>-30.634416</v>
       </c>
       <c r="O49">
-        <v>-5.909239800000001</v>
+        <v>-6.126883200000001</v>
       </c>
       <c r="P49">
-        <v>-23.6369592</v>
+        <v>-24.5075328</v>
       </c>
       <c r="Q49">
-        <v>-45.2369592</v>
+        <v>-46.1075328</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08837469312148893</v>
+        <v>0.0891934372199791</v>
       </c>
       <c r="T49">
-        <v>0.8076261961922249</v>
+        <v>0.8231574691959215</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08446375457929924</v>
+        <v>0.08270409302556385</v>
       </c>
       <c r="W49">
-        <v>0.2158834466702013</v>
+        <v>0.2162983748645721</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4223187728964962</v>
+        <v>0.4135204651278191</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1502038072893837</v>
+        <v>0.1521038072893837</v>
       </c>
       <c r="C50">
-        <v>-52.35819416248879</v>
+        <v>-59.15282168776568</v>
       </c>
       <c r="D50">
-        <v>143.7618058375112</v>
+        <v>141.5821783122343</v>
       </c>
       <c r="E50">
-        <v>-21.28</v>
+        <v>-16.66499999999999</v>
       </c>
       <c r="F50">
-        <v>221.52</v>
+        <v>226.135</v>
       </c>
       <c r="G50">
         <v>25.4</v>
@@ -5367,37 +5367,37 @@
         <v>21.6</v>
       </c>
       <c r="M50">
-        <v>52.234416</v>
+        <v>53.322633</v>
       </c>
       <c r="N50">
-        <v>-30.63441599999999</v>
+        <v>-31.722633</v>
       </c>
       <c r="O50">
-        <v>-6.126883199999999</v>
+        <v>-6.344526600000001</v>
       </c>
       <c r="P50">
-        <v>-24.5075328</v>
+        <v>-25.3781064</v>
       </c>
       <c r="Q50">
-        <v>-46.1075328</v>
+        <v>-46.9781064</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0891934372199791</v>
+        <v>0.09004428893017474</v>
       </c>
       <c r="T50">
-        <v>0.8231574691959215</v>
+        <v>0.8392978117291746</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08270409302556386</v>
+        <v>0.08101625439238908</v>
       </c>
       <c r="W50">
-        <v>0.2162983748645721</v>
+        <v>0.2166963672142747</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4135204651278193</v>
+        <v>0.4050812719619453</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5413,22 +5413,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1521038072893837</v>
+        <v>0.1540038072893837</v>
       </c>
       <c r="C51">
-        <v>-59.15282168776568</v>
+        <v>-65.88234397131018</v>
       </c>
       <c r="D51">
-        <v>141.5821783122343</v>
+        <v>139.4676560286898</v>
       </c>
       <c r="E51">
-        <v>-16.66499999999999</v>
+        <v>-12.04999999999998</v>
       </c>
       <c r="F51">
-        <v>226.135</v>
+        <v>230.75</v>
       </c>
       <c r="G51">
         <v>25.4</v>
@@ -5449,37 +5449,37 @@
         <v>21.6</v>
       </c>
       <c r="M51">
-        <v>53.322633</v>
+        <v>54.41085</v>
       </c>
       <c r="N51">
-        <v>-31.722633</v>
+        <v>-32.81085</v>
       </c>
       <c r="O51">
-        <v>-6.344526600000001</v>
+        <v>-6.562170000000001</v>
       </c>
       <c r="P51">
-        <v>-25.3781064</v>
+        <v>-26.24868</v>
       </c>
       <c r="Q51">
-        <v>-46.9781064</v>
+        <v>-47.84868</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09004428893017474</v>
+        <v>0.09092917470877826</v>
       </c>
       <c r="T51">
-        <v>0.8392978117291746</v>
+        <v>0.8560837679637583</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08101625439238908</v>
+        <v>0.07939592930454129</v>
       </c>
       <c r="W51">
-        <v>0.2166963672142747</v>
+        <v>0.2170784398699892</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4050812719619453</v>
+        <v>0.3969796465227065</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5495,22 +5495,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1540038072893837</v>
+        <v>0.1559038072893837</v>
       </c>
       <c r="C52">
-        <v>-65.88234397131018</v>
+        <v>-72.54963511845298</v>
       </c>
       <c r="D52">
-        <v>139.4676560286898</v>
+        <v>137.415364881547</v>
       </c>
       <c r="E52">
-        <v>-12.04999999999998</v>
+        <v>-7.434999999999974</v>
       </c>
       <c r="F52">
-        <v>230.75</v>
+        <v>235.365</v>
       </c>
       <c r="G52">
         <v>25.4</v>
@@ -5531,37 +5531,37 @@
         <v>21.6</v>
       </c>
       <c r="M52">
-        <v>54.41085</v>
+        <v>55.499067</v>
       </c>
       <c r="N52">
-        <v>-32.81085</v>
+        <v>-33.899067</v>
       </c>
       <c r="O52">
-        <v>-6.562170000000001</v>
+        <v>-6.779813400000001</v>
       </c>
       <c r="P52">
-        <v>-26.24868</v>
+        <v>-27.1192536</v>
       </c>
       <c r="Q52">
-        <v>-47.84868</v>
+        <v>-48.7192536</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09092917470877826</v>
+        <v>0.09185017827426353</v>
       </c>
       <c r="T52">
-        <v>0.8560837679637583</v>
+        <v>0.8735548652691411</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07939592930454129</v>
+        <v>0.07783914637700126</v>
       </c>
       <c r="W52">
-        <v>0.2170784398699892</v>
+        <v>0.2174455292843031</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3969796465227065</v>
+        <v>0.3891957318850063</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1559038072893837</v>
+        <v>0.1578038072893837</v>
       </c>
       <c r="C53">
-        <v>-72.54963511845298</v>
+        <v>-79.15740251595224</v>
       </c>
       <c r="D53">
-        <v>137.415364881547</v>
+        <v>135.4225974840478</v>
       </c>
       <c r="E53">
-        <v>-7.434999999999974</v>
+        <v>-2.819999999999965</v>
       </c>
       <c r="F53">
-        <v>235.365</v>
+        <v>239.98</v>
       </c>
       <c r="G53">
         <v>25.4</v>
@@ -5613,37 +5613,37 @@
         <v>21.6</v>
       </c>
       <c r="M53">
-        <v>55.499067</v>
+        <v>56.587284</v>
       </c>
       <c r="N53">
-        <v>-33.899067</v>
+        <v>-34.987284</v>
       </c>
       <c r="O53">
-        <v>-6.779813400000001</v>
+        <v>-6.997456800000001</v>
       </c>
       <c r="P53">
-        <v>-27.1192536</v>
+        <v>-27.9898272</v>
       </c>
       <c r="Q53">
-        <v>-48.7192536</v>
+        <v>-49.5898272</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09185017827426353</v>
+        <v>0.09280955698831068</v>
       </c>
       <c r="T53">
-        <v>0.8735548652691411</v>
+        <v>0.8917539249622483</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07783914637700126</v>
+        <v>0.07634223971590509</v>
       </c>
       <c r="W53">
-        <v>0.2174455292843031</v>
+        <v>0.2177984998749896</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3891957318850063</v>
+        <v>0.3817111985795254</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5659,22 +5659,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1578038072893837</v>
+        <v>0.1597038072893837</v>
       </c>
       <c r="C54">
-        <v>-79.15740251595224</v>
+        <v>-85.70819874777249</v>
       </c>
       <c r="D54">
-        <v>135.4225974840478</v>
+        <v>133.4868012522275</v>
       </c>
       <c r="E54">
-        <v>-2.819999999999965</v>
+        <v>1.795000000000016</v>
       </c>
       <c r="F54">
-        <v>239.98</v>
+        <v>244.595</v>
       </c>
       <c r="G54">
         <v>25.4</v>
@@ -5695,37 +5695,37 @@
         <v>21.6</v>
       </c>
       <c r="M54">
-        <v>56.587284</v>
+        <v>57.675501</v>
       </c>
       <c r="N54">
-        <v>-34.987284</v>
+        <v>-36.075501</v>
       </c>
       <c r="O54">
-        <v>-6.997456800000001</v>
+        <v>-7.215100200000001</v>
       </c>
       <c r="P54">
-        <v>-27.9898272</v>
+        <v>-28.8604008</v>
       </c>
       <c r="Q54">
-        <v>-49.5898272</v>
+        <v>-50.4604008</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09280955698831068</v>
+        <v>0.09380976032848751</v>
       </c>
       <c r="T54">
-        <v>0.8917539249622483</v>
+        <v>0.9107274127274025</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07634223971590509</v>
+        <v>0.07490182009862385</v>
       </c>
       <c r="W54">
-        <v>0.2177984998749896</v>
+        <v>0.2181381508207445</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3817111985795254</v>
+        <v>0.3745091004931193</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5741,22 +5741,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1597038072893837</v>
+        <v>0.1616038072893837</v>
       </c>
       <c r="C55">
-        <v>-85.70819874777249</v>
+        <v>-92.20443250328887</v>
       </c>
       <c r="D55">
-        <v>133.4868012522275</v>
+        <v>131.6055674967111</v>
       </c>
       <c r="E55">
-        <v>1.795000000000016</v>
+        <v>6.410000000000025</v>
       </c>
       <c r="F55">
-        <v>244.595</v>
+        <v>249.21</v>
       </c>
       <c r="G55">
         <v>25.4</v>
@@ -5777,37 +5777,37 @@
         <v>21.6</v>
       </c>
       <c r="M55">
-        <v>57.675501</v>
+        <v>58.763718</v>
       </c>
       <c r="N55">
-        <v>-36.075501</v>
+        <v>-37.163718</v>
       </c>
       <c r="O55">
-        <v>-7.215100200000001</v>
+        <v>-7.432743600000001</v>
       </c>
       <c r="P55">
-        <v>-28.8604008</v>
+        <v>-29.7309744</v>
       </c>
       <c r="Q55">
-        <v>-50.4604008</v>
+        <v>-51.3309744</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09380976032848751</v>
+        <v>0.09485345077041116</v>
       </c>
       <c r="T55">
-        <v>0.9107274127274025</v>
+        <v>0.9305258347432156</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07490182009862385</v>
+        <v>0.07351474935605674</v>
       </c>
       <c r="W55">
-        <v>0.2181381508207445</v>
+        <v>0.2184652221018418</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3745091004931193</v>
+        <v>0.3675737467802838</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5823,22 +5823,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1616038072893837</v>
+        <v>0.1635038072893837</v>
       </c>
       <c r="C56">
-        <v>-92.20443250328887</v>
+        <v>-98.64837857593105</v>
       </c>
       <c r="D56">
-        <v>131.6055674967111</v>
+        <v>129.776621424069</v>
       </c>
       <c r="E56">
-        <v>6.410000000000025</v>
+        <v>11.02500000000003</v>
       </c>
       <c r="F56">
-        <v>249.21</v>
+        <v>253.825</v>
       </c>
       <c r="G56">
         <v>25.4</v>
@@ -5859,37 +5859,37 @@
         <v>21.6</v>
       </c>
       <c r="M56">
-        <v>58.763718</v>
+        <v>59.851935</v>
       </c>
       <c r="N56">
-        <v>-37.163718</v>
+        <v>-38.251935</v>
       </c>
       <c r="O56">
-        <v>-7.432743600000001</v>
+        <v>-7.650387000000001</v>
       </c>
       <c r="P56">
-        <v>-29.7309744</v>
+        <v>-30.601548</v>
       </c>
       <c r="Q56">
-        <v>-51.3309744</v>
+        <v>-52.201548</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09485345077041116</v>
+        <v>0.09594352745419807</v>
       </c>
       <c r="T56">
-        <v>0.9305258347432156</v>
+        <v>0.9512041866263983</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07351474935605674</v>
+        <v>0.07217811754958299</v>
       </c>
       <c r="W56">
-        <v>0.2184652221018418</v>
+        <v>0.2187803998818083</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3675737467802838</v>
+        <v>0.3608905877479149</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5905,22 +5905,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1635038072893837</v>
+        <v>0.1654038072893837</v>
       </c>
       <c r="C57">
-        <v>-98.64837857593105</v>
+        <v>-105.042187039537</v>
       </c>
       <c r="D57">
-        <v>129.776621424069</v>
+        <v>127.997812960463</v>
       </c>
       <c r="E57">
-        <v>11.02500000000003</v>
+        <v>15.64000000000001</v>
       </c>
       <c r="F57">
-        <v>253.825</v>
+        <v>258.44</v>
       </c>
       <c r="G57">
         <v>25.4</v>
@@ -5941,37 +5941,37 @@
         <v>21.6</v>
       </c>
       <c r="M57">
-        <v>59.851935</v>
+        <v>60.940152</v>
       </c>
       <c r="N57">
-        <v>-38.251935</v>
+        <v>-39.340152</v>
       </c>
       <c r="O57">
-        <v>-7.650387000000001</v>
+        <v>-7.868030400000001</v>
       </c>
       <c r="P57">
-        <v>-30.601548</v>
+        <v>-31.4721216</v>
       </c>
       <c r="Q57">
-        <v>-52.201548</v>
+        <v>-53.0721216</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09594352745419807</v>
+        <v>0.09708315307815711</v>
       </c>
       <c r="T57">
-        <v>0.9512041866263983</v>
+        <v>0.9728224635951799</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07217811754958299</v>
+        <v>0.07088922259334043</v>
       </c>
       <c r="W57">
-        <v>0.2187803998818083</v>
+        <v>0.2190843213124903</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3608905877479149</v>
+        <v>0.3544461129667021</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5987,22 +5987,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1654038072893837</v>
+        <v>0.1673038072893837</v>
       </c>
       <c r="C58">
-        <v>-105.042187039537</v>
+        <v>-111.3878916802466</v>
       </c>
       <c r="D58">
-        <v>127.997812960463</v>
+        <v>126.2671083197534</v>
       </c>
       <c r="E58">
-        <v>15.64000000000001</v>
+        <v>20.25500000000002</v>
       </c>
       <c r="F58">
-        <v>258.44</v>
+        <v>263.055</v>
       </c>
       <c r="G58">
         <v>25.4</v>
@@ -6023,37 +6023,37 @@
         <v>21.6</v>
       </c>
       <c r="M58">
-        <v>60.940152</v>
+        <v>62.028369</v>
       </c>
       <c r="N58">
-        <v>-39.340152</v>
+        <v>-40.428369</v>
       </c>
       <c r="O58">
-        <v>-7.868030400000001</v>
+        <v>-8.0856738</v>
       </c>
       <c r="P58">
-        <v>-31.4721216</v>
+        <v>-32.3426952</v>
       </c>
       <c r="Q58">
-        <v>-53.0721216</v>
+        <v>-53.9426952</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09708315307815711</v>
+        <v>0.09827578454509101</v>
       </c>
       <c r="T58">
-        <v>0.9728224635951799</v>
+        <v>0.9954462418183236</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07088922259334043</v>
+        <v>0.06964555202152743</v>
       </c>
       <c r="W58">
-        <v>0.2190843213124903</v>
+        <v>0.2193775788333238</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3544461129667021</v>
+        <v>0.3482277601076372</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6069,22 +6069,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1673038072893837</v>
+        <v>0.1692038072893837</v>
       </c>
       <c r="C59">
-        <v>-111.3878916802466</v>
+        <v>-117.6874177534559</v>
       </c>
       <c r="D59">
-        <v>126.2671083197534</v>
+        <v>124.5825822465441</v>
       </c>
       <c r="E59">
-        <v>20.25500000000002</v>
+        <v>24.87000000000003</v>
       </c>
       <c r="F59">
-        <v>263.055</v>
+        <v>267.67</v>
       </c>
       <c r="G59">
         <v>25.4</v>
@@ -6105,37 +6105,37 @@
         <v>21.6</v>
       </c>
       <c r="M59">
-        <v>62.028369</v>
+        <v>63.11658600000001</v>
       </c>
       <c r="N59">
-        <v>-40.428369</v>
+        <v>-41.516586</v>
       </c>
       <c r="O59">
-        <v>-8.0856738</v>
+        <v>-8.3033172</v>
       </c>
       <c r="P59">
-        <v>-32.3426952</v>
+        <v>-33.2132688</v>
       </c>
       <c r="Q59">
-        <v>-53.9426952</v>
+        <v>-54.8132688</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09827578454509101</v>
+        <v>0.09952520798664079</v>
       </c>
       <c r="T59">
-        <v>0.9954462418183236</v>
+        <v>1.019147342813998</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06964555202152743</v>
+        <v>0.06844476664184594</v>
       </c>
       <c r="W59">
-        <v>0.2193775788333238</v>
+        <v>0.2196607240258527</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3482277601076372</v>
+        <v>0.3422238332092297</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6151,22 +6151,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1692038072893837</v>
+        <v>0.1711038072893837</v>
       </c>
       <c r="C60">
-        <v>-117.6874177534557</v>
+        <v>-123.9425891280357</v>
       </c>
       <c r="D60">
-        <v>124.5825822465442</v>
+        <v>122.9424108719643</v>
       </c>
       <c r="E60">
-        <v>24.86999999999998</v>
+        <v>29.48499999999999</v>
       </c>
       <c r="F60">
-        <v>267.67</v>
+        <v>272.285</v>
       </c>
       <c r="G60">
         <v>25.4</v>
@@ -6187,37 +6187,37 @@
         <v>21.6</v>
       </c>
       <c r="M60">
-        <v>63.11658599999999</v>
+        <v>64.204803</v>
       </c>
       <c r="N60">
-        <v>-41.51658599999999</v>
+        <v>-42.604803</v>
       </c>
       <c r="O60">
-        <v>-8.303317199999999</v>
+        <v>-8.5209606</v>
       </c>
       <c r="P60">
-        <v>-33.21326879999999</v>
+        <v>-34.08384239999999</v>
       </c>
       <c r="Q60">
-        <v>-54.8132688</v>
+        <v>-55.6838424</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09952520798664077</v>
+        <v>0.1008355789131442</v>
       </c>
       <c r="T60">
-        <v>1.019147342813998</v>
+        <v>1.044004595077754</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06844476664184594</v>
+        <v>0.06728468585130619</v>
       </c>
       <c r="W60">
-        <v>0.2196607240258527</v>
+        <v>0.219934271076262</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3422238332092298</v>
+        <v>0.3364234292565309</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6233,22 +6233,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1711038072893837</v>
+        <v>0.1730038072893837</v>
       </c>
       <c r="C61">
-        <v>-123.9425891280357</v>
+        <v>-130.155134873546</v>
       </c>
       <c r="D61">
-        <v>122.9424108719643</v>
+        <v>121.3448651264539</v>
       </c>
       <c r="E61">
-        <v>29.48499999999999</v>
+        <v>34.09999999999999</v>
       </c>
       <c r="F61">
-        <v>272.285</v>
+        <v>276.9</v>
       </c>
       <c r="G61">
         <v>25.4</v>
@@ -6269,37 +6269,37 @@
         <v>21.6</v>
       </c>
       <c r="M61">
-        <v>64.204803</v>
+        <v>65.29302</v>
       </c>
       <c r="N61">
-        <v>-42.604803</v>
+        <v>-43.69302</v>
       </c>
       <c r="O61">
-        <v>-8.5209606</v>
+        <v>-8.738604</v>
       </c>
       <c r="P61">
-        <v>-34.08384239999999</v>
+        <v>-34.95441599999999</v>
       </c>
       <c r="Q61">
-        <v>-55.6838424</v>
+        <v>-56.554416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1008355789131442</v>
+        <v>0.1022114683859728</v>
       </c>
       <c r="T61">
-        <v>1.044004595077754</v>
+        <v>1.070104709954698</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06728468585130619</v>
+        <v>0.06616327442045108</v>
       </c>
       <c r="W61">
-        <v>0.219934271076262</v>
+        <v>0.2201986998916576</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3364234292565309</v>
+        <v>0.3308163721022553</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6315,22 +6315,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1730038072893837</v>
+        <v>0.1749038072893837</v>
       </c>
       <c r="C62">
-        <v>-130.155134873546</v>
+        <v>-136.3266953404629</v>
       </c>
       <c r="D62">
-        <v>121.3448651264539</v>
+        <v>119.7883046595371</v>
       </c>
       <c r="E62">
-        <v>34.09999999999999</v>
+        <v>38.715</v>
       </c>
       <c r="F62">
-        <v>276.9</v>
+        <v>281.515</v>
       </c>
       <c r="G62">
         <v>25.4</v>
@@ -6351,37 +6351,37 @@
         <v>21.6</v>
       </c>
       <c r="M62">
-        <v>65.29302</v>
+        <v>66.381237</v>
       </c>
       <c r="N62">
-        <v>-43.69302</v>
+        <v>-44.781237</v>
       </c>
       <c r="O62">
-        <v>-8.738604</v>
+        <v>-8.956247400000001</v>
       </c>
       <c r="P62">
-        <v>-34.95441599999999</v>
+        <v>-35.82498959999999</v>
       </c>
       <c r="Q62">
-        <v>-56.554416</v>
+        <v>-57.4249896</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1022114683859728</v>
+        <v>0.1036579162933055</v>
       </c>
       <c r="T62">
-        <v>1.070104709954698</v>
+        <v>1.097543292261228</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06616327442045108</v>
+        <v>0.06507863057749286</v>
       </c>
       <c r="W62">
-        <v>0.2201986998916576</v>
+        <v>0.2204544589098272</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3308163721022553</v>
+        <v>0.3253931528874643</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1749038072893837</v>
+        <v>0.1768038072893837</v>
       </c>
       <c r="C63">
-        <v>-136.3266953404629</v>
+        <v>-142.4588277783643</v>
       </c>
       <c r="D63">
-        <v>119.7883046595371</v>
+        <v>118.2711722216357</v>
       </c>
       <c r="E63">
-        <v>38.715</v>
+        <v>43.33000000000001</v>
       </c>
       <c r="F63">
-        <v>281.515</v>
+        <v>286.13</v>
       </c>
       <c r="G63">
         <v>25.4</v>
@@ -6433,37 +6433,37 @@
         <v>21.6</v>
       </c>
       <c r="M63">
-        <v>66.381237</v>
+        <v>67.469454</v>
       </c>
       <c r="N63">
-        <v>-44.781237</v>
+        <v>-45.869454</v>
       </c>
       <c r="O63">
-        <v>-8.956247400000001</v>
+        <v>-9.173890800000001</v>
       </c>
       <c r="P63">
-        <v>-35.82498959999999</v>
+        <v>-36.6955632</v>
       </c>
       <c r="Q63">
-        <v>-57.4249896</v>
+        <v>-58.2955632</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1036579162933055</v>
+        <v>0.1051804930378661</v>
       </c>
       <c r="T63">
-        <v>1.097543292261228</v>
+        <v>1.126426010478629</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06507863057749286</v>
+        <v>0.06402897524559781</v>
       </c>
       <c r="W63">
-        <v>0.2204544589098272</v>
+        <v>0.220701967637088</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3253931528874643</v>
+        <v>0.320144876227989</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6479,22 +6479,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1768038072893837</v>
+        <v>0.1787038072893837</v>
       </c>
       <c r="C64">
-        <v>-142.4588277783643</v>
+        <v>-148.5530115325263</v>
       </c>
       <c r="D64">
-        <v>118.2711722216357</v>
+        <v>116.7919884674737</v>
       </c>
       <c r="E64">
-        <v>43.33000000000001</v>
+        <v>47.94500000000002</v>
       </c>
       <c r="F64">
-        <v>286.13</v>
+        <v>290.745</v>
       </c>
       <c r="G64">
         <v>25.4</v>
@@ -6515,37 +6515,37 @@
         <v>21.6</v>
       </c>
       <c r="M64">
-        <v>67.469454</v>
+        <v>68.557671</v>
       </c>
       <c r="N64">
-        <v>-45.869454</v>
+        <v>-46.957671</v>
       </c>
       <c r="O64">
-        <v>-9.173890800000001</v>
+        <v>-9.391534200000001</v>
       </c>
       <c r="P64">
-        <v>-36.6955632</v>
+        <v>-37.5661368</v>
       </c>
       <c r="Q64">
-        <v>-58.2955632</v>
+        <v>-59.1661368</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1051804930378661</v>
+        <v>0.1067853712280787</v>
       </c>
       <c r="T64">
-        <v>1.126426010478629</v>
+        <v>1.156869956707781</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06402897524559781</v>
+        <v>0.0630126423051915</v>
       </c>
       <c r="W64">
-        <v>0.220701967637088</v>
+        <v>0.2209416189444358</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.320144876227989</v>
+        <v>0.3150632115259575</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6561,22 +6561,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1787038072893837</v>
+        <v>0.1806038072893837</v>
       </c>
       <c r="C65">
-        <v>-148.5530115325263</v>
+        <v>-154.6106528553822</v>
       </c>
       <c r="D65">
-        <v>116.7919884674737</v>
+        <v>115.3493471446178</v>
       </c>
       <c r="E65">
-        <v>47.94500000000002</v>
+        <v>52.56000000000003</v>
       </c>
       <c r="F65">
-        <v>290.745</v>
+        <v>295.36</v>
       </c>
       <c r="G65">
         <v>25.4</v>
@@ -6597,37 +6597,37 @@
         <v>21.6</v>
       </c>
       <c r="M65">
-        <v>68.557671</v>
+        <v>69.645888</v>
       </c>
       <c r="N65">
-        <v>-46.957671</v>
+        <v>-48.045888</v>
       </c>
       <c r="O65">
-        <v>-9.391534200000001</v>
+        <v>-9.609177600000001</v>
       </c>
       <c r="P65">
-        <v>-37.5661368</v>
+        <v>-38.4367104</v>
       </c>
       <c r="Q65">
-        <v>-59.1661368</v>
+        <v>-60.0367104</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1067853712280787</v>
+        <v>0.1084794093177476</v>
       </c>
       <c r="T65">
-        <v>1.156869956707781</v>
+        <v>1.189005233282998</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0630126423051915</v>
+        <v>0.06202806976917288</v>
       </c>
       <c r="W65">
-        <v>0.2209416189444358</v>
+        <v>0.2211737811484291</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3150632115259575</v>
+        <v>0.3101403488458644</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6643,22 +6643,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1806038072893837</v>
+        <v>0.1825038072893837</v>
       </c>
       <c r="C66">
-        <v>-154.6106528553822</v>
+        <v>-160.6330893657375</v>
       </c>
       <c r="D66">
-        <v>115.3493471446178</v>
+        <v>113.9419106342625</v>
       </c>
       <c r="E66">
-        <v>52.56000000000003</v>
+        <v>57.17500000000004</v>
       </c>
       <c r="F66">
-        <v>295.36</v>
+        <v>299.975</v>
       </c>
       <c r="G66">
         <v>25.4</v>
@@ -6679,37 +6679,37 @@
         <v>21.6</v>
       </c>
       <c r="M66">
-        <v>69.645888</v>
+        <v>70.73410500000001</v>
       </c>
       <c r="N66">
-        <v>-48.045888</v>
+        <v>-49.13410500000001</v>
       </c>
       <c r="O66">
-        <v>-9.609177600000001</v>
+        <v>-9.826821000000002</v>
       </c>
       <c r="P66">
-        <v>-38.4367104</v>
+        <v>-39.30728400000001</v>
       </c>
       <c r="Q66">
-        <v>-60.0367104</v>
+        <v>-60.90728400000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1084794093177476</v>
+        <v>0.1102702495839689</v>
       </c>
       <c r="T66">
-        <v>1.189005233282998</v>
+        <v>1.222976811376798</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06202806976917288</v>
+        <v>0.06107379177272405</v>
       </c>
       <c r="W66">
-        <v>0.2211737811484291</v>
+        <v>0.2213987998999917</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3101403488458644</v>
+        <v>0.3053689588636203</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6725,22 +6725,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1825038072893837</v>
+        <v>0.1844038072893837</v>
       </c>
       <c r="C67">
-        <v>-160.6330893657375</v>
+        <v>-166.6215941854678</v>
       </c>
       <c r="D67">
-        <v>113.9419106342625</v>
+        <v>112.5684058145322</v>
       </c>
       <c r="E67">
-        <v>57.17500000000004</v>
+        <v>61.79000000000005</v>
       </c>
       <c r="F67">
-        <v>299.975</v>
+        <v>304.59</v>
       </c>
       <c r="G67">
         <v>25.4</v>
@@ -6761,37 +6761,37 @@
         <v>21.6</v>
       </c>
       <c r="M67">
-        <v>70.73410500000001</v>
+        <v>71.82232200000001</v>
       </c>
       <c r="N67">
-        <v>-49.13410500000001</v>
+        <v>-50.22232200000001</v>
       </c>
       <c r="O67">
-        <v>-9.826821000000002</v>
+        <v>-10.0444644</v>
       </c>
       <c r="P67">
-        <v>-39.30728400000001</v>
+        <v>-40.17785760000001</v>
       </c>
       <c r="Q67">
-        <v>-60.90728400000001</v>
+        <v>-61.77785760000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1102702495839689</v>
+        <v>0.1121664333952621</v>
       </c>
       <c r="T67">
-        <v>1.222976811376798</v>
+        <v>1.258946717593762</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06107379177272405</v>
+        <v>0.06014843129131915</v>
       </c>
       <c r="W67">
-        <v>0.2213987998999917</v>
+        <v>0.2216169999015069</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3053689588636203</v>
+        <v>0.3007421564565957</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6807,22 +6807,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1844038072893837</v>
+        <v>0.1863038072893837</v>
       </c>
       <c r="C68">
-        <v>-166.6215941854678</v>
+        <v>-172.5773797805846</v>
       </c>
       <c r="D68">
-        <v>112.5684058145322</v>
+        <v>111.2276202194155</v>
       </c>
       <c r="E68">
-        <v>61.79000000000005</v>
+        <v>66.40500000000006</v>
       </c>
       <c r="F68">
-        <v>304.59</v>
+        <v>309.205</v>
       </c>
       <c r="G68">
         <v>25.4</v>
@@ -6843,37 +6843,37 @@
         <v>21.6</v>
       </c>
       <c r="M68">
-        <v>71.82232200000001</v>
+        <v>72.91053900000001</v>
       </c>
       <c r="N68">
-        <v>-50.22232200000001</v>
+        <v>-51.31053900000001</v>
       </c>
       <c r="O68">
-        <v>-10.0444644</v>
+        <v>-10.2621078</v>
       </c>
       <c r="P68">
-        <v>-40.17785760000001</v>
+        <v>-41.04843120000001</v>
       </c>
       <c r="Q68">
-        <v>-61.77785760000001</v>
+        <v>-62.64843120000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1121664333952621</v>
+        <v>0.1141775374375428</v>
       </c>
       <c r="T68">
-        <v>1.258946717593762</v>
+        <v>1.297096618126907</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06014843129131915</v>
+        <v>0.05925069351085169</v>
       </c>
       <c r="W68">
-        <v>0.2216169999015069</v>
+        <v>0.2218286864701412</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3007421564565957</v>
+        <v>0.2962534675542585</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6889,22 +6889,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1863038072893837</v>
+        <v>0.1882038072893837</v>
       </c>
       <c r="C69">
-        <v>-172.5773797805846</v>
+        <v>-178.5016015310312</v>
       </c>
       <c r="D69">
-        <v>111.2276202194155</v>
+        <v>109.9183984689688</v>
       </c>
       <c r="E69">
-        <v>66.40500000000006</v>
+        <v>71.02000000000007</v>
       </c>
       <c r="F69">
-        <v>309.205</v>
+        <v>313.8200000000001</v>
       </c>
       <c r="G69">
         <v>25.4</v>
@@ -6925,37 +6925,37 @@
         <v>21.6</v>
       </c>
       <c r="M69">
-        <v>72.91053900000001</v>
+        <v>73.99875600000001</v>
       </c>
       <c r="N69">
-        <v>-51.31053900000001</v>
+        <v>-52.39875600000001</v>
       </c>
       <c r="O69">
-        <v>-10.2621078</v>
+        <v>-10.4797512</v>
       </c>
       <c r="P69">
-        <v>-41.04843120000001</v>
+        <v>-41.91900480000001</v>
       </c>
       <c r="Q69">
-        <v>-62.64843120000001</v>
+        <v>-63.51900480000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1141775374375428</v>
+        <v>0.116314335482466</v>
       </c>
       <c r="T69">
-        <v>1.297096618126907</v>
+        <v>1.337630887443372</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05925069351085169</v>
+        <v>0.05837935978275094</v>
       </c>
       <c r="W69">
-        <v>0.2218286864701412</v>
+        <v>0.2220341469632273</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2962534675542585</v>
+        <v>0.2918967989137546</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6971,22 +6971,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1882038072893837</v>
+        <v>0.1901038072893838</v>
       </c>
       <c r="C70">
-        <v>-178.5016015310312</v>
+        <v>-184.395361051299</v>
       </c>
       <c r="D70">
-        <v>109.9183984689688</v>
+        <v>108.639638948701</v>
       </c>
       <c r="E70">
-        <v>71.02000000000007</v>
+        <v>75.63500000000002</v>
       </c>
       <c r="F70">
-        <v>313.8200000000001</v>
+        <v>318.435</v>
       </c>
       <c r="G70">
         <v>25.4</v>
@@ -7007,37 +7007,37 @@
         <v>21.6</v>
       </c>
       <c r="M70">
-        <v>73.99875600000001</v>
+        <v>75.086973</v>
       </c>
       <c r="N70">
-        <v>-52.39875600000001</v>
+        <v>-53.486973</v>
       </c>
       <c r="O70">
-        <v>-10.4797512</v>
+        <v>-10.6973946</v>
       </c>
       <c r="P70">
-        <v>-41.91900480000001</v>
+        <v>-42.7895784</v>
       </c>
       <c r="Q70">
-        <v>-63.51900480000001</v>
+        <v>-64.3895784</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.116314335482466</v>
+        <v>0.1185889914657714</v>
       </c>
       <c r="T70">
-        <v>1.337630887443372</v>
+        <v>1.380780270909288</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05837935978275094</v>
+        <v>0.05753328210474006</v>
       </c>
       <c r="W70">
-        <v>0.2220341469632273</v>
+        <v>0.2222336520797023</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2918967989137546</v>
+        <v>0.2876664105237003</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7053,22 +7053,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1901038072893838</v>
+        <v>0.1920038072893837</v>
       </c>
       <c r="C71">
-        <v>-184.395361051299</v>
+        <v>-190.2597092819215</v>
       </c>
       <c r="D71">
-        <v>108.639638948701</v>
+        <v>107.3902907180785</v>
       </c>
       <c r="E71">
-        <v>75.63500000000002</v>
+        <v>80.25000000000003</v>
       </c>
       <c r="F71">
-        <v>318.435</v>
+        <v>323.05</v>
       </c>
       <c r="G71">
         <v>25.4</v>
@@ -7089,37 +7089,37 @@
         <v>21.6</v>
       </c>
       <c r="M71">
-        <v>75.086973</v>
+        <v>76.17519</v>
       </c>
       <c r="N71">
-        <v>-53.486973</v>
+        <v>-54.57519</v>
       </c>
       <c r="O71">
-        <v>-10.6973946</v>
+        <v>-10.915038</v>
       </c>
       <c r="P71">
-        <v>-42.7895784</v>
+        <v>-43.660152</v>
       </c>
       <c r="Q71">
-        <v>-64.3895784</v>
+        <v>-65.26015200000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1185889914657714</v>
+        <v>0.1210152911812971</v>
       </c>
       <c r="T71">
-        <v>1.380780270909288</v>
+        <v>1.426806279939598</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05753328210474006</v>
+        <v>0.05671137807467235</v>
       </c>
       <c r="W71">
-        <v>0.2222336520797023</v>
+        <v>0.2224274570499923</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2876664105237003</v>
+        <v>0.2835568903733617</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7135,22 +7135,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1920038072893837</v>
+        <v>0.1939038072893837</v>
       </c>
       <c r="C72">
-        <v>-190.2597092819215</v>
+        <v>-196.0956493700828</v>
       </c>
       <c r="D72">
-        <v>107.3902907180785</v>
+        <v>106.1693506299172</v>
       </c>
       <c r="E72">
-        <v>80.25000000000003</v>
+        <v>84.86500000000004</v>
       </c>
       <c r="F72">
-        <v>323.05</v>
+        <v>327.665</v>
       </c>
       <c r="G72">
         <v>25.4</v>
@@ -7171,37 +7171,37 @@
         <v>21.6</v>
       </c>
       <c r="M72">
-        <v>76.17519</v>
+        <v>77.26340700000002</v>
       </c>
       <c r="N72">
-        <v>-54.57519</v>
+        <v>-55.66340700000001</v>
       </c>
       <c r="O72">
-        <v>-10.915038</v>
+        <v>-11.1326814</v>
       </c>
       <c r="P72">
-        <v>-43.660152</v>
+        <v>-44.53072560000001</v>
       </c>
       <c r="Q72">
-        <v>-65.26015200000001</v>
+        <v>-66.13072560000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1210152911812971</v>
+        <v>0.1236089219116867</v>
       </c>
       <c r="T72">
-        <v>1.426806279939598</v>
+        <v>1.476006496489239</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05671137807467235</v>
+        <v>0.05591262627080371</v>
       </c>
       <c r="W72">
-        <v>0.2224274570499923</v>
+        <v>0.2226158027253445</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2835568903733617</v>
+        <v>0.2795631313540186</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7217,22 +7217,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1939038072893837</v>
+        <v>0.1958038072893837</v>
       </c>
       <c r="C73">
-        <v>-196.0956493700828</v>
+        <v>-201.904139355933</v>
       </c>
       <c r="D73">
-        <v>106.1693506299172</v>
+        <v>104.975860644067</v>
       </c>
       <c r="E73">
-        <v>84.86499999999998</v>
+        <v>89.47999999999999</v>
       </c>
       <c r="F73">
-        <v>327.665</v>
+        <v>332.28</v>
       </c>
       <c r="G73">
         <v>25.4</v>
@@ -7253,37 +7253,37 @@
         <v>21.6</v>
       </c>
       <c r="M73">
-        <v>77.263407</v>
+        <v>78.351624</v>
       </c>
       <c r="N73">
-        <v>-55.663407</v>
+        <v>-56.751624</v>
       </c>
       <c r="O73">
-        <v>-11.1326814</v>
+        <v>-11.3503248</v>
       </c>
       <c r="P73">
-        <v>-44.5307256</v>
+        <v>-45.4012992</v>
       </c>
       <c r="Q73">
-        <v>-66.13072560000001</v>
+        <v>-67.00129920000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1236089219116867</v>
+        <v>0.1263878119799612</v>
       </c>
       <c r="T73">
-        <v>1.476006496489238</v>
+        <v>1.528721014220997</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05591262627080373</v>
+        <v>0.05513606201704257</v>
       </c>
       <c r="W73">
-        <v>0.2226158027253445</v>
+        <v>0.2227989165763814</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2795631313540187</v>
+        <v>0.2756803100852128</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7299,22 +7299,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1958038072893837</v>
+        <v>0.1977038072893837</v>
       </c>
       <c r="C74">
-        <v>-201.904139355933</v>
+        <v>-207.6860946797315</v>
       </c>
       <c r="D74">
-        <v>104.975860644067</v>
+        <v>103.8089053202685</v>
       </c>
       <c r="E74">
-        <v>89.47999999999999</v>
+        <v>94.095</v>
       </c>
       <c r="F74">
-        <v>332.28</v>
+        <v>336.895</v>
       </c>
       <c r="G74">
         <v>25.4</v>
@@ -7335,37 +7335,37 @@
         <v>21.6</v>
       </c>
       <c r="M74">
-        <v>78.351624</v>
+        <v>79.439841</v>
       </c>
       <c r="N74">
-        <v>-56.751624</v>
+        <v>-57.839841</v>
       </c>
       <c r="O74">
-        <v>-11.3503248</v>
+        <v>-11.5679682</v>
       </c>
       <c r="P74">
-        <v>-45.4012992</v>
+        <v>-46.2718728</v>
       </c>
       <c r="Q74">
-        <v>-67.00129920000001</v>
+        <v>-67.87187280000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1263878119799612</v>
+        <v>0.1293725457569968</v>
       </c>
       <c r="T74">
-        <v>1.528721014220997</v>
+        <v>1.585340311043997</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05513606201704257</v>
+        <v>0.05438077349626116</v>
       </c>
       <c r="W74">
-        <v>0.2227989165763814</v>
+        <v>0.2229770136095816</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2756803100852128</v>
+        <v>0.2719038674813058</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7381,22 +7381,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1977038072893837</v>
+        <v>0.1996038072893837</v>
       </c>
       <c r="C75">
-        <v>-207.6860946797315</v>
+        <v>-213.4423905236053</v>
       </c>
       <c r="D75">
-        <v>103.8089053202685</v>
+        <v>102.6676094763947</v>
       </c>
       <c r="E75">
-        <v>94.095</v>
+        <v>98.71000000000001</v>
       </c>
       <c r="F75">
-        <v>336.895</v>
+        <v>341.51</v>
       </c>
       <c r="G75">
         <v>25.4</v>
@@ -7417,37 +7417,37 @@
         <v>21.6</v>
       </c>
       <c r="M75">
-        <v>79.439841</v>
+        <v>80.528058</v>
       </c>
       <c r="N75">
-        <v>-57.839841</v>
+        <v>-58.928058</v>
       </c>
       <c r="O75">
-        <v>-11.5679682</v>
+        <v>-11.7856116</v>
       </c>
       <c r="P75">
-        <v>-46.2718728</v>
+        <v>-47.1424464</v>
       </c>
       <c r="Q75">
-        <v>-67.87187280000001</v>
+        <v>-68.74244640000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1293725457569968</v>
+        <v>0.1325868744399582</v>
       </c>
       <c r="T75">
-        <v>1.585340311043997</v>
+        <v>1.646314938391843</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05438077349626116</v>
+        <v>0.05364589817874411</v>
       </c>
       <c r="W75">
-        <v>0.2229770136095816</v>
+        <v>0.2231502972094521</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2719038674813058</v>
+        <v>0.2682294908937206</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7463,22 +7463,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1996038072893837</v>
+        <v>0.2015038072893837</v>
       </c>
       <c r="C76">
-        <v>-213.4423905236053</v>
+        <v>-219.1738640005128</v>
       </c>
       <c r="D76">
-        <v>102.6676094763947</v>
+        <v>101.5511359994872</v>
       </c>
       <c r="E76">
-        <v>98.71000000000001</v>
+        <v>103.325</v>
       </c>
       <c r="F76">
-        <v>341.51</v>
+        <v>346.125</v>
       </c>
       <c r="G76">
         <v>25.4</v>
@@ -7499,37 +7499,37 @@
         <v>21.6</v>
       </c>
       <c r="M76">
-        <v>80.528058</v>
+        <v>81.616275</v>
       </c>
       <c r="N76">
-        <v>-58.928058</v>
+        <v>-60.016275</v>
       </c>
       <c r="O76">
-        <v>-11.7856116</v>
+        <v>-12.003255</v>
       </c>
       <c r="P76">
-        <v>-47.1424464</v>
+        <v>-48.01302</v>
       </c>
       <c r="Q76">
-        <v>-68.74244640000001</v>
+        <v>-69.61302000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1325868744399582</v>
+        <v>0.1360583494175565</v>
       </c>
       <c r="T76">
-        <v>1.646314938391843</v>
+        <v>1.712167535927517</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05364589817874411</v>
+        <v>0.05293061953636086</v>
       </c>
       <c r="W76">
-        <v>0.2231502972094521</v>
+        <v>0.2233189599133261</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2682294908937206</v>
+        <v>0.2646530976818043</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7545,22 +7545,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2015038072893837</v>
+        <v>0.2034038072893837</v>
       </c>
       <c r="C77">
-        <v>-219.1738640005128</v>
+        <v>-224.8813162019189</v>
       </c>
       <c r="D77">
-        <v>101.5511359994872</v>
+        <v>100.4586837980811</v>
       </c>
       <c r="E77">
-        <v>103.325</v>
+        <v>107.94</v>
       </c>
       <c r="F77">
-        <v>346.125</v>
+        <v>350.74</v>
       </c>
       <c r="G77">
         <v>25.4</v>
@@ -7581,37 +7581,37 @@
         <v>21.6</v>
       </c>
       <c r="M77">
-        <v>81.616275</v>
+        <v>82.704492</v>
       </c>
       <c r="N77">
-        <v>-60.016275</v>
+        <v>-61.104492</v>
       </c>
       <c r="O77">
-        <v>-12.003255</v>
+        <v>-12.2208984</v>
       </c>
       <c r="P77">
-        <v>-48.01302</v>
+        <v>-48.8835936</v>
       </c>
       <c r="Q77">
-        <v>-69.61302000000001</v>
+        <v>-70.48359360000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1360583494175565</v>
+        <v>0.1398191139766214</v>
       </c>
       <c r="T77">
-        <v>1.712167535927517</v>
+        <v>1.783507849924497</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05293061953636086</v>
+        <v>0.05223416401614558</v>
       </c>
       <c r="W77">
-        <v>0.2233189599133261</v>
+        <v>0.2234831841249929</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2646530976818043</v>
+        <v>0.2611708200807279</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7627,22 +7627,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2034038072893837</v>
+        <v>0.2053038072893837</v>
       </c>
       <c r="C78">
-        <v>-224.8813162019189</v>
+        <v>-230.565514114708</v>
       </c>
       <c r="D78">
-        <v>100.4586837980811</v>
+        <v>99.38948588529207</v>
       </c>
       <c r="E78">
-        <v>107.94</v>
+        <v>112.555</v>
       </c>
       <c r="F78">
-        <v>350.74</v>
+        <v>355.355</v>
       </c>
       <c r="G78">
         <v>25.4</v>
@@ -7663,37 +7663,37 @@
         <v>21.6</v>
       </c>
       <c r="M78">
-        <v>82.704492</v>
+        <v>83.792709</v>
       </c>
       <c r="N78">
-        <v>-61.104492</v>
+        <v>-62.192709</v>
       </c>
       <c r="O78">
-        <v>-12.2208984</v>
+        <v>-12.4385418</v>
       </c>
       <c r="P78">
-        <v>-48.8835936</v>
+        <v>-49.7541672</v>
       </c>
       <c r="Q78">
-        <v>-70.48359360000001</v>
+        <v>-71.35416720000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1398191139766214</v>
+        <v>0.1439069015408223</v>
       </c>
       <c r="T78">
-        <v>1.783507849924497</v>
+        <v>1.861051669486431</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05223416401614558</v>
+        <v>0.05155579824970213</v>
       </c>
       <c r="W78">
-        <v>0.2234831841249929</v>
+        <v>0.2236431427727202</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2611708200807279</v>
+        <v>0.2577789912485107</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7709,22 +7709,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2053038072893837</v>
+        <v>0.2072038072893837</v>
       </c>
       <c r="C79">
-        <v>-230.565514114708</v>
+        <v>-236.2271924169733</v>
       </c>
       <c r="D79">
-        <v>99.38948588529207</v>
+        <v>98.34280758302673</v>
       </c>
       <c r="E79">
-        <v>112.555</v>
+        <v>117.17</v>
       </c>
       <c r="F79">
-        <v>355.355</v>
+        <v>359.97</v>
       </c>
       <c r="G79">
         <v>25.4</v>
@@ -7745,37 +7745,37 @@
         <v>21.6</v>
       </c>
       <c r="M79">
-        <v>83.792709</v>
+        <v>84.88092600000002</v>
       </c>
       <c r="N79">
-        <v>-62.192709</v>
+        <v>-63.28092600000002</v>
       </c>
       <c r="O79">
-        <v>-12.4385418</v>
+        <v>-12.6561852</v>
       </c>
       <c r="P79">
-        <v>-49.7541672</v>
+        <v>-50.62474080000001</v>
       </c>
       <c r="Q79">
-        <v>-71.35416720000001</v>
+        <v>-72.22474080000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1439069015408223</v>
+        <v>0.1483663061563142</v>
       </c>
       <c r="T79">
-        <v>1.861051669486431</v>
+        <v>1.94564492719036</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05155579824970213</v>
+        <v>0.05089482647727005</v>
       </c>
       <c r="W79">
-        <v>0.2236431427727202</v>
+        <v>0.2237989999166597</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2577789912485107</v>
+        <v>0.2544741323863502</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7791,22 +7791,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2072038072893837</v>
+        <v>0.2091038072893837</v>
       </c>
       <c r="C80">
-        <v>-236.2271924169733</v>
+        <v>-241.8670551615201</v>
       </c>
       <c r="D80">
-        <v>98.34280758302673</v>
+        <v>97.31794483847995</v>
       </c>
       <c r="E80">
-        <v>117.17</v>
+        <v>121.7850000000001</v>
       </c>
       <c r="F80">
-        <v>359.97</v>
+        <v>364.585</v>
       </c>
       <c r="G80">
         <v>25.4</v>
@@ -7827,37 +7827,37 @@
         <v>21.6</v>
       </c>
       <c r="M80">
-        <v>84.88092600000002</v>
+        <v>85.96914300000002</v>
       </c>
       <c r="N80">
-        <v>-63.28092600000002</v>
+        <v>-64.36914300000001</v>
       </c>
       <c r="O80">
-        <v>-12.6561852</v>
+        <v>-12.8738286</v>
       </c>
       <c r="P80">
-        <v>-50.62474080000001</v>
+        <v>-51.49531440000001</v>
       </c>
       <c r="Q80">
-        <v>-72.22474080000001</v>
+        <v>-73.09531440000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1483663061563142</v>
+        <v>0.1532504159732816</v>
       </c>
       <c r="T80">
-        <v>1.94564492719036</v>
+        <v>2.038294685627996</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05089482647727005</v>
+        <v>0.05025058816743119</v>
       </c>
       <c r="W80">
-        <v>0.2237989999166597</v>
+        <v>0.2239509113101197</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2544741323863502</v>
+        <v>0.251252940837156</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7873,22 +7873,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2091038072893837</v>
+        <v>0.2110038072893837</v>
       </c>
       <c r="C81">
-        <v>-241.8670551615201</v>
+        <v>-247.4857773551876</v>
       </c>
       <c r="D81">
-        <v>97.31794483847995</v>
+        <v>96.31422264481249</v>
       </c>
       <c r="E81">
-        <v>121.7850000000001</v>
+        <v>126.4000000000001</v>
       </c>
       <c r="F81">
-        <v>364.585</v>
+        <v>369.2</v>
       </c>
       <c r="G81">
         <v>25.4</v>
@@ -7909,37 +7909,37 @@
         <v>21.6</v>
       </c>
       <c r="M81">
-        <v>85.96914300000002</v>
+        <v>87.05736000000002</v>
       </c>
       <c r="N81">
-        <v>-64.36914300000001</v>
+        <v>-65.45736000000002</v>
       </c>
       <c r="O81">
-        <v>-12.8738286</v>
+        <v>-13.091472</v>
       </c>
       <c r="P81">
-        <v>-51.49531440000001</v>
+        <v>-52.36588800000002</v>
       </c>
       <c r="Q81">
-        <v>-73.09531440000001</v>
+        <v>-73.96588800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1532504159732816</v>
+        <v>0.1586229367719456</v>
       </c>
       <c r="T81">
-        <v>2.038294685627996</v>
+        <v>2.140209419909396</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05025058816743119</v>
+        <v>0.0496224558153383</v>
       </c>
       <c r="W81">
-        <v>0.2239509113101197</v>
+        <v>0.2240990249187432</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.251252940837156</v>
+        <v>0.2481122790766914</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2110038072893837</v>
+        <v>0.2129038072893837</v>
       </c>
       <c r="C82">
-        <v>-247.4857773551876</v>
+        <v>-253.0840064414357</v>
       </c>
       <c r="D82">
-        <v>96.31422264481249</v>
+        <v>95.33099355856426</v>
       </c>
       <c r="E82">
-        <v>126.4000000000001</v>
+        <v>131.015</v>
       </c>
       <c r="F82">
-        <v>369.2</v>
+        <v>373.815</v>
       </c>
       <c r="G82">
         <v>25.4</v>
@@ -7991,37 +7991,37 @@
         <v>21.6</v>
       </c>
       <c r="M82">
-        <v>87.05736000000002</v>
+        <v>88.145577</v>
       </c>
       <c r="N82">
-        <v>-65.45736000000002</v>
+        <v>-66.54557700000001</v>
       </c>
       <c r="O82">
-        <v>-13.091472</v>
+        <v>-13.3091154</v>
       </c>
       <c r="P82">
-        <v>-52.36588800000002</v>
+        <v>-53.23646160000001</v>
       </c>
       <c r="Q82">
-        <v>-73.96588800000002</v>
+        <v>-74.83646160000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1586229367719456</v>
+        <v>0.1645609860757323</v>
       </c>
       <c r="T82">
-        <v>2.140209419909396</v>
+        <v>2.252852020957259</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0496224558153383</v>
+        <v>0.04900983290403783</v>
       </c>
       <c r="W82">
-        <v>0.2240990249187432</v>
+        <v>0.2242434814012279</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2481122790766914</v>
+        <v>0.2450491645201891</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8037,22 +8037,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2129038072893837</v>
+        <v>0.2148038072893837</v>
       </c>
       <c r="C83">
-        <v>-253.0840064414357</v>
+        <v>-258.66236369304</v>
       </c>
       <c r="D83">
-        <v>95.33099355856426</v>
+        <v>94.36763630696004</v>
       </c>
       <c r="E83">
-        <v>131.015</v>
+        <v>135.63</v>
       </c>
       <c r="F83">
-        <v>373.815</v>
+        <v>378.43</v>
       </c>
       <c r="G83">
         <v>25.4</v>
@@ -8073,37 +8073,37 @@
         <v>21.6</v>
       </c>
       <c r="M83">
-        <v>88.145577</v>
+        <v>89.233794</v>
       </c>
       <c r="N83">
-        <v>-66.54557700000001</v>
+        <v>-67.63379399999999</v>
       </c>
       <c r="O83">
-        <v>-13.3091154</v>
+        <v>-13.5267588</v>
       </c>
       <c r="P83">
-        <v>-53.23646160000001</v>
+        <v>-54.1070352</v>
       </c>
       <c r="Q83">
-        <v>-74.83646160000001</v>
+        <v>-75.70703520000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1645609860757323</v>
+        <v>0.1711588186354952</v>
       </c>
       <c r="T83">
-        <v>2.252852020957259</v>
+        <v>2.378010466565996</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04900983290403783</v>
+        <v>0.0484121520149642</v>
       </c>
       <c r="W83">
-        <v>0.2242434814012279</v>
+        <v>0.2243844145548715</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2450491645201891</v>
+        <v>0.242060760074821</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8119,22 +8119,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2148038072893837</v>
+        <v>0.2167038072893837</v>
       </c>
       <c r="C84">
-        <v>-258.66236369304</v>
+        <v>-264.2214455211866</v>
       </c>
       <c r="D84">
-        <v>94.36763630696004</v>
+        <v>93.42355447881336</v>
       </c>
       <c r="E84">
-        <v>135.63</v>
+        <v>140.245</v>
       </c>
       <c r="F84">
-        <v>378.43</v>
+        <v>383.045</v>
       </c>
       <c r="G84">
         <v>25.4</v>
@@ -8155,37 +8155,37 @@
         <v>21.6</v>
       </c>
       <c r="M84">
-        <v>89.233794</v>
+        <v>90.322011</v>
       </c>
       <c r="N84">
-        <v>-67.63379399999999</v>
+        <v>-68.72201100000001</v>
       </c>
       <c r="O84">
-        <v>-13.5267588</v>
+        <v>-13.7444022</v>
       </c>
       <c r="P84">
-        <v>-54.1070352</v>
+        <v>-54.97760880000001</v>
       </c>
       <c r="Q84">
-        <v>-75.70703520000001</v>
+        <v>-76.57760880000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1711588186354952</v>
+        <v>0.1785328667905243</v>
       </c>
       <c r="T84">
-        <v>2.378010466565996</v>
+        <v>2.517893435187525</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0484121520149642</v>
+        <v>0.04782887307502487</v>
       </c>
       <c r="W84">
-        <v>0.2243844145548715</v>
+        <v>0.2245219517289091</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.242060760074821</v>
+        <v>0.2391443653751243</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8201,22 +8201,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2167038072893837</v>
+        <v>0.2186038072893838</v>
       </c>
       <c r="C85">
-        <v>-264.2214455211866</v>
+        <v>-269.7618247067689</v>
       </c>
       <c r="D85">
-        <v>93.42355447881336</v>
+        <v>92.49817529323111</v>
       </c>
       <c r="E85">
-        <v>140.245</v>
+        <v>144.86</v>
       </c>
       <c r="F85">
-        <v>383.045</v>
+        <v>387.66</v>
       </c>
       <c r="G85">
         <v>25.4</v>
@@ -8237,37 +8237,37 @@
         <v>21.6</v>
       </c>
       <c r="M85">
-        <v>90.322011</v>
+        <v>91.410228</v>
       </c>
       <c r="N85">
-        <v>-68.72201100000001</v>
+        <v>-69.810228</v>
       </c>
       <c r="O85">
-        <v>-13.7444022</v>
+        <v>-13.9620456</v>
       </c>
       <c r="P85">
-        <v>-54.97760880000001</v>
+        <v>-55.8481824</v>
       </c>
       <c r="Q85">
-        <v>-76.57760880000001</v>
+        <v>-77.44818240000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1785328667905243</v>
+        <v>0.1868286709649321</v>
       </c>
       <c r="T85">
-        <v>2.517893435187525</v>
+        <v>2.675261774886746</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04782887307502487</v>
+        <v>0.04725948172889363</v>
       </c>
       <c r="W85">
-        <v>0.2245219517289091</v>
+        <v>0.2246562142083269</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2391443653751243</v>
+        <v>0.2362974086444681</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8283,22 +8283,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2186038072893837</v>
+        <v>0.2205038072893837</v>
       </c>
       <c r="C86">
-        <v>-269.7618247067689</v>
+        <v>-275.2840515592225</v>
       </c>
       <c r="D86">
-        <v>92.49817529323106</v>
+        <v>91.5909484407775</v>
       </c>
       <c r="E86">
-        <v>144.86</v>
+        <v>149.475</v>
       </c>
       <c r="F86">
-        <v>387.66</v>
+        <v>392.275</v>
       </c>
       <c r="G86">
         <v>25.4</v>
@@ -8319,37 +8319,37 @@
         <v>21.6</v>
       </c>
       <c r="M86">
-        <v>91.41022799999999</v>
+        <v>92.498445</v>
       </c>
       <c r="N86">
-        <v>-69.810228</v>
+        <v>-70.89844500000001</v>
       </c>
       <c r="O86">
-        <v>-13.9620456</v>
+        <v>-14.179689</v>
       </c>
       <c r="P86">
-        <v>-55.8481824</v>
+        <v>-56.71875600000001</v>
       </c>
       <c r="Q86">
-        <v>-77.44818240000001</v>
+        <v>-78.31875600000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1868286709649321</v>
+        <v>0.1962305823625942</v>
       </c>
       <c r="T86">
-        <v>2.675261774886744</v>
+        <v>2.853612559879194</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04725948172889363</v>
+        <v>0.04670348782620076</v>
       </c>
       <c r="W86">
-        <v>0.2246562142083269</v>
+        <v>0.2247873175705819</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.236297408644468</v>
+        <v>0.2335174391310036</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8365,22 +8365,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2205038072893837</v>
+        <v>0.2224038072893837</v>
       </c>
       <c r="C87">
-        <v>-275.2840515592225</v>
+        <v>-280.7886550078277</v>
       </c>
       <c r="D87">
-        <v>91.5909484407775</v>
+        <v>90.70134499217224</v>
       </c>
       <c r="E87">
-        <v>149.475</v>
+        <v>154.09</v>
       </c>
       <c r="F87">
-        <v>392.275</v>
+        <v>396.89</v>
       </c>
       <c r="G87">
         <v>25.4</v>
@@ -8401,37 +8401,37 @@
         <v>21.6</v>
       </c>
       <c r="M87">
-        <v>92.498445</v>
+        <v>93.586662</v>
       </c>
       <c r="N87">
-        <v>-70.89844500000001</v>
+        <v>-71.986662</v>
       </c>
       <c r="O87">
-        <v>-14.179689</v>
+        <v>-14.3973324</v>
       </c>
       <c r="P87">
-        <v>-56.71875600000001</v>
+        <v>-57.5893296</v>
       </c>
       <c r="Q87">
-        <v>-78.31875600000001</v>
+        <v>-79.18932960000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1962305823625942</v>
+        <v>0.2069756239599223</v>
       </c>
       <c r="T87">
-        <v>2.853612559879194</v>
+        <v>3.057442028441994</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04670348782620076</v>
+        <v>0.04616042401426819</v>
       </c>
       <c r="W87">
-        <v>0.2247873175705819</v>
+        <v>0.2249153720174356</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2335174391310036</v>
+        <v>0.230802120071341</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8447,22 +8447,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2224038072893837</v>
+        <v>0.2243038072893837</v>
       </c>
       <c r="C88">
-        <v>-280.7886550078277</v>
+        <v>-286.2761436300268</v>
       </c>
       <c r="D88">
-        <v>90.70134499217224</v>
+        <v>89.82885636997322</v>
       </c>
       <c r="E88">
-        <v>154.09</v>
+        <v>158.705</v>
       </c>
       <c r="F88">
-        <v>396.89</v>
+        <v>401.505</v>
       </c>
       <c r="G88">
         <v>25.4</v>
@@ -8483,37 +8483,37 @@
         <v>21.6</v>
       </c>
       <c r="M88">
-        <v>93.586662</v>
+        <v>94.674879</v>
       </c>
       <c r="N88">
-        <v>-71.986662</v>
+        <v>-73.07487900000001</v>
       </c>
       <c r="O88">
-        <v>-14.3973324</v>
+        <v>-14.6149758</v>
       </c>
       <c r="P88">
-        <v>-57.5893296</v>
+        <v>-58.45990320000001</v>
       </c>
       <c r="Q88">
-        <v>-79.18932960000001</v>
+        <v>-80.05990320000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2069756239599223</v>
+        <v>0.2193737488799164</v>
       </c>
       <c r="T88">
-        <v>3.057442028441994</v>
+        <v>3.292629876783685</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04616042401426819</v>
+        <v>0.04562984442789729</v>
       </c>
       <c r="W88">
-        <v>0.2249153720174356</v>
+        <v>0.2250404826839018</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.230802120071341</v>
+        <v>0.2281492221394864</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8529,22 +8529,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2243038072893837</v>
+        <v>0.2262038072893837</v>
       </c>
       <c r="C89">
-        <v>-286.2761436300268</v>
+        <v>-291.747006620955</v>
       </c>
       <c r="D89">
-        <v>89.82885636997322</v>
+        <v>88.97299337904501</v>
       </c>
       <c r="E89">
-        <v>158.705</v>
+        <v>163.32</v>
       </c>
       <c r="F89">
-        <v>401.505</v>
+        <v>406.12</v>
       </c>
       <c r="G89">
         <v>25.4</v>
@@ -8565,37 +8565,37 @@
         <v>21.6</v>
       </c>
       <c r="M89">
-        <v>94.674879</v>
+        <v>95.763096</v>
       </c>
       <c r="N89">
-        <v>-73.07487900000001</v>
+        <v>-74.163096</v>
       </c>
       <c r="O89">
-        <v>-14.6149758</v>
+        <v>-14.8326192</v>
       </c>
       <c r="P89">
-        <v>-58.45990320000001</v>
+        <v>-59.3304768</v>
       </c>
       <c r="Q89">
-        <v>-80.05990320000001</v>
+        <v>-80.93047680000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2193737488799164</v>
+        <v>0.2338382279532427</v>
       </c>
       <c r="T89">
-        <v>3.292629876783685</v>
+        <v>3.567015699848993</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04562984442789729</v>
+        <v>0.04511132346848937</v>
       </c>
       <c r="W89">
-        <v>0.2250404826839018</v>
+        <v>0.2251627499261302</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2281492221394864</v>
+        <v>0.2255566173424469</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8611,22 +8611,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2262038072893837</v>
+        <v>0.2281038072893837</v>
       </c>
       <c r="C90">
-        <v>-291.747006620955</v>
+        <v>-297.2017147080712</v>
       </c>
       <c r="D90">
-        <v>88.97299337904501</v>
+        <v>88.13328529192877</v>
       </c>
       <c r="E90">
-        <v>163.32</v>
+        <v>167.935</v>
       </c>
       <c r="F90">
-        <v>406.12</v>
+        <v>410.735</v>
       </c>
       <c r="G90">
         <v>25.4</v>
@@ -8647,37 +8647,37 @@
         <v>21.6</v>
       </c>
       <c r="M90">
-        <v>95.763096</v>
+        <v>96.851313</v>
       </c>
       <c r="N90">
-        <v>-74.163096</v>
+        <v>-75.25131300000001</v>
       </c>
       <c r="O90">
-        <v>-14.8326192</v>
+        <v>-15.0502626</v>
       </c>
       <c r="P90">
-        <v>-59.3304768</v>
+        <v>-60.20105040000001</v>
       </c>
       <c r="Q90">
-        <v>-80.93047680000001</v>
+        <v>-81.80105040000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2338382279532427</v>
+        <v>0.2509326123126284</v>
       </c>
       <c r="T90">
-        <v>3.567015699848993</v>
+        <v>3.89128985438072</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04511132346848937</v>
+        <v>0.04460445466547264</v>
       </c>
       <c r="W90">
-        <v>0.2251627499261302</v>
+        <v>0.2252822695898815</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2255566173424469</v>
+        <v>0.2230222733273631</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8693,22 +8693,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2281038072893837</v>
+        <v>0.2300038072893837</v>
       </c>
       <c r="C91">
-        <v>-297.2017147080712</v>
+        <v>-302.6407210144804</v>
       </c>
       <c r="D91">
-        <v>88.13328529192877</v>
+        <v>87.30927898551961</v>
       </c>
       <c r="E91">
-        <v>167.935</v>
+        <v>172.55</v>
       </c>
       <c r="F91">
-        <v>410.735</v>
+        <v>415.35</v>
       </c>
       <c r="G91">
         <v>25.4</v>
@@ -8729,37 +8729,37 @@
         <v>21.6</v>
       </c>
       <c r="M91">
-        <v>96.851313</v>
+        <v>97.93953</v>
       </c>
       <c r="N91">
-        <v>-75.25131300000001</v>
+        <v>-76.33953</v>
       </c>
       <c r="O91">
-        <v>-15.0502626</v>
+        <v>-15.267906</v>
       </c>
       <c r="P91">
-        <v>-60.20105040000001</v>
+        <v>-61.071624</v>
       </c>
       <c r="Q91">
-        <v>-81.80105040000001</v>
+        <v>-82.67162400000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2509326123126284</v>
+        <v>0.2714458735438913</v>
       </c>
       <c r="T91">
-        <v>3.89128985438072</v>
+        <v>4.280418839818792</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04460445466547264</v>
+        <v>0.04410884961363404</v>
       </c>
       <c r="W91">
-        <v>0.2252822695898815</v>
+        <v>0.2253991332611051</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2230222733273631</v>
+        <v>0.2205442480681703</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8775,22 +8775,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2300038072893837</v>
+        <v>0.2319038072893838</v>
       </c>
       <c r="C92">
-        <v>-302.6407210144804</v>
+        <v>-308.0644618742735</v>
       </c>
       <c r="D92">
-        <v>87.30927898551961</v>
+        <v>86.50053812572651</v>
       </c>
       <c r="E92">
-        <v>172.55</v>
+        <v>177.165</v>
       </c>
       <c r="F92">
-        <v>415.35</v>
+        <v>419.965</v>
       </c>
       <c r="G92">
         <v>25.4</v>
@@ -8811,37 +8811,37 @@
         <v>21.6</v>
       </c>
       <c r="M92">
-        <v>97.93953</v>
+        <v>99.02774700000001</v>
       </c>
       <c r="N92">
-        <v>-76.33953</v>
+        <v>-77.42774700000001</v>
       </c>
       <c r="O92">
-        <v>-15.267906</v>
+        <v>-15.4855494</v>
       </c>
       <c r="P92">
-        <v>-61.071624</v>
+        <v>-61.94219760000001</v>
       </c>
       <c r="Q92">
-        <v>-82.67162400000001</v>
+        <v>-83.54219760000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2714458735438913</v>
+        <v>0.2965176372709905</v>
       </c>
       <c r="T92">
-        <v>4.280418839818792</v>
+        <v>4.756020933131992</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04410884961363404</v>
+        <v>0.04362413698051719</v>
       </c>
       <c r="W92">
-        <v>0.2253991332611051</v>
+        <v>0.2255134284999941</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2205442480681703</v>
+        <v>0.2181206849025858</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8857,22 +8857,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2319038072893838</v>
+        <v>0.2338038072893837</v>
       </c>
       <c r="C93">
-        <v>-308.0644618742735</v>
+        <v>-313.4733576029697</v>
       </c>
       <c r="D93">
-        <v>86.50053812572651</v>
+        <v>85.70664239703032</v>
       </c>
       <c r="E93">
-        <v>177.165</v>
+        <v>181.7800000000001</v>
       </c>
       <c r="F93">
-        <v>419.965</v>
+        <v>424.58</v>
       </c>
       <c r="G93">
         <v>25.4</v>
@@ -8893,37 +8893,37 @@
         <v>21.6</v>
       </c>
       <c r="M93">
-        <v>99.02774700000001</v>
+        <v>100.115964</v>
       </c>
       <c r="N93">
-        <v>-77.42774700000001</v>
+        <v>-78.51596400000003</v>
       </c>
       <c r="O93">
-        <v>-15.4855494</v>
+        <v>-15.70319280000001</v>
       </c>
       <c r="P93">
-        <v>-61.94219760000001</v>
+        <v>-62.81277120000002</v>
       </c>
       <c r="Q93">
-        <v>-83.54219760000001</v>
+        <v>-84.41277120000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2965176372709905</v>
+        <v>0.3278573419298643</v>
       </c>
       <c r="T93">
-        <v>4.756020933131992</v>
+        <v>5.350523549773492</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04362413698051719</v>
+        <v>0.04314996157855504</v>
       </c>
       <c r="W93">
-        <v>0.2255134284999941</v>
+        <v>0.2256252390597767</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2181206849025858</v>
+        <v>0.2157498078927751</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8939,22 +8939,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2338038072893837</v>
+        <v>0.2357038072893837</v>
       </c>
       <c r="C94">
-        <v>-313.4733576029697</v>
+        <v>-318.8678132259179</v>
       </c>
       <c r="D94">
-        <v>85.70664239703032</v>
+        <v>84.92718677408216</v>
       </c>
       <c r="E94">
-        <v>181.7800000000001</v>
+        <v>186.3950000000001</v>
       </c>
       <c r="F94">
-        <v>424.58</v>
+        <v>429.1950000000001</v>
       </c>
       <c r="G94">
         <v>25.4</v>
@@ -8975,37 +8975,37 @@
         <v>21.6</v>
       </c>
       <c r="M94">
-        <v>100.115964</v>
+        <v>101.204181</v>
       </c>
       <c r="N94">
-        <v>-78.51596400000003</v>
+        <v>-79.60418100000001</v>
       </c>
       <c r="O94">
-        <v>-15.70319280000001</v>
+        <v>-15.9208362</v>
       </c>
       <c r="P94">
-        <v>-62.81277120000002</v>
+        <v>-63.68334480000001</v>
       </c>
       <c r="Q94">
-        <v>-84.41277120000002</v>
+        <v>-85.28334480000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3278573419298643</v>
+        <v>0.3681512479198449</v>
       </c>
       <c r="T94">
-        <v>5.350523549773492</v>
+        <v>6.114884056883992</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04314996157855504</v>
+        <v>0.04268598349706521</v>
       </c>
       <c r="W94">
-        <v>0.2256252390597767</v>
+        <v>0.225734645091392</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2157498078927751</v>
+        <v>0.213429917485326</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2357038072893837</v>
+        <v>0.2376038072893837</v>
       </c>
       <c r="C95">
-        <v>-318.8678132259179</v>
+        <v>-324.2482191673089</v>
       </c>
       <c r="D95">
-        <v>84.92718677408216</v>
+        <v>84.16178083269115</v>
       </c>
       <c r="E95">
-        <v>186.3950000000001</v>
+        <v>191.01</v>
       </c>
       <c r="F95">
-        <v>429.1950000000001</v>
+        <v>433.81</v>
       </c>
       <c r="G95">
         <v>25.4</v>
@@ -9057,37 +9057,37 @@
         <v>21.6</v>
       </c>
       <c r="M95">
-        <v>101.204181</v>
+        <v>102.292398</v>
       </c>
       <c r="N95">
-        <v>-79.60418100000001</v>
+        <v>-80.692398</v>
       </c>
       <c r="O95">
-        <v>-15.9208362</v>
+        <v>-16.1384796</v>
       </c>
       <c r="P95">
-        <v>-63.68334480000001</v>
+        <v>-64.5539184</v>
       </c>
       <c r="Q95">
-        <v>-85.28334480000001</v>
+        <v>-86.15391840000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3681512479198449</v>
+        <v>0.4218764559064858</v>
       </c>
       <c r="T95">
-        <v>6.114884056883992</v>
+        <v>7.134031399697992</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04268598349706521</v>
+        <v>0.04223187728964962</v>
       </c>
       <c r="W95">
-        <v>0.225734645091392</v>
+        <v>0.2258417233351006</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.213429917485326</v>
+        <v>0.2111593864482482</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9103,22 +9103,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2376038072893837</v>
+        <v>0.2395038072893838</v>
       </c>
       <c r="C96">
-        <v>-324.2482191673089</v>
+        <v>-329.6149519022639</v>
       </c>
       <c r="D96">
-        <v>84.16178083269115</v>
+        <v>83.41004809773608</v>
       </c>
       <c r="E96">
-        <v>191.01</v>
+        <v>195.625</v>
       </c>
       <c r="F96">
-        <v>433.81</v>
+        <v>438.425</v>
       </c>
       <c r="G96">
         <v>25.4</v>
@@ -9139,37 +9139,37 @@
         <v>21.6</v>
       </c>
       <c r="M96">
-        <v>102.292398</v>
+        <v>103.380615</v>
       </c>
       <c r="N96">
-        <v>-80.692398</v>
+        <v>-81.78061500000001</v>
       </c>
       <c r="O96">
-        <v>-16.1384796</v>
+        <v>-16.356123</v>
       </c>
       <c r="P96">
-        <v>-64.5539184</v>
+        <v>-65.42449200000001</v>
       </c>
       <c r="Q96">
-        <v>-86.15391840000001</v>
+        <v>-87.02449200000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4218764559064858</v>
+        <v>0.4970917470877833</v>
       </c>
       <c r="T96">
-        <v>7.134031399697992</v>
+        <v>8.560837679637595</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04223187728964962</v>
+        <v>0.04178733121291647</v>
       </c>
       <c r="W96">
-        <v>0.2258417233351006</v>
+        <v>0.2259465472999943</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2111593864482482</v>
+        <v>0.2089366560645822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9185,22 +9185,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2395038072893838</v>
+        <v>0.2414038072893837</v>
       </c>
       <c r="C97">
-        <v>-329.6149519022639</v>
+        <v>-334.9683745742841</v>
       </c>
       <c r="D97">
-        <v>83.41004809773608</v>
+        <v>82.6716254257159</v>
       </c>
       <c r="E97">
-        <v>195.625</v>
+        <v>200.24</v>
       </c>
       <c r="F97">
-        <v>438.425</v>
+        <v>443.04</v>
       </c>
       <c r="G97">
         <v>25.4</v>
@@ -9221,37 +9221,37 @@
         <v>21.6</v>
       </c>
       <c r="M97">
-        <v>103.380615</v>
+        <v>104.468832</v>
       </c>
       <c r="N97">
-        <v>-81.78061500000001</v>
+        <v>-82.868832</v>
       </c>
       <c r="O97">
-        <v>-16.356123</v>
+        <v>-16.5737664</v>
       </c>
       <c r="P97">
-        <v>-65.42449200000001</v>
+        <v>-66.2950656</v>
       </c>
       <c r="Q97">
-        <v>-87.02449200000001</v>
+        <v>-87.89506560000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4970917470877833</v>
+        <v>0.6099146838597291</v>
       </c>
       <c r="T97">
-        <v>8.560837679637595</v>
+        <v>10.701047099547</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04178733121291647</v>
+        <v>0.04135204651278192</v>
       </c>
       <c r="W97">
-        <v>0.2259465472999943</v>
+        <v>0.226049187432286</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2089366560645822</v>
+        <v>0.2067602325639096</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9267,22 +9267,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2414038072893837</v>
+        <v>0.2433038072893837</v>
       </c>
       <c r="C98">
-        <v>-334.9683745742841</v>
+        <v>-340.3088375801912</v>
       </c>
       <c r="D98">
-        <v>82.6716254257159</v>
+        <v>81.9461624198088</v>
       </c>
       <c r="E98">
-        <v>200.24</v>
+        <v>204.855</v>
       </c>
       <c r="F98">
-        <v>443.04</v>
+        <v>447.655</v>
       </c>
       <c r="G98">
         <v>25.4</v>
@@ -9303,37 +9303,37 @@
         <v>21.6</v>
       </c>
       <c r="M98">
-        <v>104.468832</v>
+        <v>105.557049</v>
       </c>
       <c r="N98">
-        <v>-82.868832</v>
+        <v>-83.95704899999998</v>
       </c>
       <c r="O98">
-        <v>-16.5737664</v>
+        <v>-16.7914098</v>
       </c>
       <c r="P98">
-        <v>-66.2950656</v>
+        <v>-67.16563919999999</v>
       </c>
       <c r="Q98">
-        <v>-87.89506560000001</v>
+        <v>-88.76563919999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6099146838597277</v>
+        <v>0.7979529118129702</v>
       </c>
       <c r="T98">
-        <v>10.70104709954697</v>
+        <v>14.26806279939596</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04135204651278193</v>
+        <v>0.04092573675491819</v>
       </c>
       <c r="W98">
-        <v>0.226049187432286</v>
+        <v>0.2261497112731903</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2067602325639095</v>
+        <v>0.204628683774591</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9349,22 +9349,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2433038072893837</v>
+        <v>0.2452038072893837</v>
       </c>
       <c r="C99">
-        <v>-340.3088375801912</v>
+        <v>-345.6366791245379</v>
       </c>
       <c r="D99">
-        <v>81.9461624198088</v>
+        <v>81.23332087546211</v>
       </c>
       <c r="E99">
-        <v>204.855</v>
+        <v>209.47</v>
       </c>
       <c r="F99">
-        <v>447.655</v>
+        <v>452.27</v>
       </c>
       <c r="G99">
         <v>25.4</v>
@@ -9385,37 +9385,37 @@
         <v>21.6</v>
       </c>
       <c r="M99">
-        <v>105.557049</v>
+        <v>106.645266</v>
       </c>
       <c r="N99">
-        <v>-83.95704899999998</v>
+        <v>-85.045266</v>
       </c>
       <c r="O99">
-        <v>-16.7914098</v>
+        <v>-17.0090532</v>
       </c>
       <c r="P99">
-        <v>-67.16563919999999</v>
+        <v>-68.0362128</v>
       </c>
       <c r="Q99">
-        <v>-88.76563919999998</v>
+        <v>-89.63621280000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7979529118129702</v>
+        <v>1.174029367719456</v>
       </c>
       <c r="T99">
-        <v>14.26806279939596</v>
+        <v>21.40209419909394</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04092573675491819</v>
+        <v>0.04050812719619454</v>
       </c>
       <c r="W99">
-        <v>0.2261497112731903</v>
+        <v>0.2262481836071373</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.204628683774591</v>
+        <v>0.2025406359809727</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9431,22 +9431,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2452038072893837</v>
+        <v>0.2471038072893837</v>
       </c>
       <c r="C100">
-        <v>-345.6366791245379</v>
+        <v>-350.9522257453319</v>
       </c>
       <c r="D100">
-        <v>81.23332087546211</v>
+        <v>80.53277425466811</v>
       </c>
       <c r="E100">
-        <v>209.47</v>
+        <v>214.085</v>
       </c>
       <c r="F100">
-        <v>452.27</v>
+        <v>456.885</v>
       </c>
       <c r="G100">
         <v>25.4</v>
@@ -9467,37 +9467,37 @@
         <v>21.6</v>
       </c>
       <c r="M100">
-        <v>106.645266</v>
+        <v>107.733483</v>
       </c>
       <c r="N100">
-        <v>-85.045266</v>
+        <v>-86.13348300000001</v>
       </c>
       <c r="O100">
-        <v>-17.0090532</v>
+        <v>-17.2266966</v>
       </c>
       <c r="P100">
-        <v>-68.0362128</v>
+        <v>-68.90678640000002</v>
       </c>
       <c r="Q100">
-        <v>-89.63621280000001</v>
+        <v>-90.50678640000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.174029367719456</v>
+        <v>2.302258735438911</v>
       </c>
       <c r="T100">
-        <v>21.40209419909394</v>
+        <v>42.80418839818788</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04050812719619454</v>
+        <v>0.04009895419421278</v>
       </c>
       <c r="W100">
-        <v>0.2262481836071373</v>
+        <v>0.2263446666010047</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9505,91 +9505,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2025406359809727</v>
+        <v>0.2004947709710638</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2471038072893837</v>
-      </c>
-      <c r="C101">
-        <v>-350.9522257453319</v>
-      </c>
-      <c r="D101">
-        <v>80.53277425466811</v>
-      </c>
-      <c r="E101">
-        <v>214.085</v>
-      </c>
-      <c r="F101">
-        <v>456.885</v>
-      </c>
-      <c r="G101">
-        <v>25.4</v>
-      </c>
-      <c r="H101">
-        <v>218.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-21.6</v>
-      </c>
-      <c r="L101">
-        <v>21.6</v>
-      </c>
-      <c r="M101">
-        <v>107.733483</v>
-      </c>
-      <c r="N101">
-        <v>-86.13348300000001</v>
-      </c>
-      <c r="O101">
-        <v>-17.2266966</v>
-      </c>
-      <c r="P101">
-        <v>-68.90678640000002</v>
-      </c>
-      <c r="Q101">
-        <v>-90.50678640000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.302258735438911</v>
-      </c>
-      <c r="T101">
-        <v>42.80418839818788</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04009895419421278</v>
-      </c>
-      <c r="W101">
-        <v>0.2263446666010047</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2004947709710638</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
